--- a/Codebooks/Human Codebooks/content - cleaned/D - Content Analysis Codebook (cleaned) - Selene.xlsx
+++ b/Codebooks/Human Codebooks/content - cleaned/D - Content Analysis Codebook (cleaned) - Selene.xlsx
@@ -710,7 +710,7 @@
       <c r="O2" s="3" t="inlineStr"/>
       <c r="P2" s="3" t="inlineStr">
         <is>
-          <t>Kenyan or Nigerian political/social problems, Economic/status pressure, Men’s behavior</t>
+          <t>Kenyan or Nigerian political/social problems, Economic/status pressure, Men's behavior</t>
         </is>
       </c>
       <c r="Q2" s="3" t="inlineStr"/>
@@ -917,13 +917,13 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Use of all CAPS, Uses a news headline or social media trend as opener</t>
+          <t>Uses a news headline or social media trend as opener, Use of all CAPS</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr"/>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Gender issues, e.g. equality, Social issues, e.g. corruption, Money/status</t>
+          <t>Social issues, e.g. corruption, Gender issues, e.g. equality, Money/status</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr"/>
@@ -956,7 +956,7 @@
       <c r="O4" s="3" t="inlineStr"/>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t>General political/social/cultural problems</t>
+          <t>Global political/social/cultural problems</t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr"/>
@@ -1075,7 +1075,7 @@
       <c r="O5" s="3" t="inlineStr"/>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t>General political/social/cultural problems</t>
+          <t>Global political/social/cultural problems</t>
         </is>
       </c>
       <c r="Q5" s="3" t="inlineStr"/>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="W5" s="3" t="inlineStr">
         <is>
-          <t>Personal experience, Cultural/social observations</t>
+          <t>Cultural/social observations, Personal experience</t>
         </is>
       </c>
       <c r="X5" s="3" t="inlineStr"/>
@@ -1173,7 +1173,7 @@
       <c r="F6" s="3" t="inlineStr"/>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>Money/status, Gender issues, e.g. equality</t>
+          <t>Gender issues, e.g. equality, Money/status</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr"/>
@@ -1292,7 +1292,7 @@
       <c r="F7" s="3" t="inlineStr"/>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>Dating/marriage, Family/children, Gender issues, e.g. equality, Money/status</t>
+          <t>Gender issues, e.g. equality, Dating/marriage, Family/children, Money/status</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr"/>
@@ -1325,7 +1325,7 @@
       <c r="O7" s="3" t="inlineStr"/>
       <c r="P7" s="3" t="inlineStr">
         <is>
-          <t>Men’s behavior, Economic/status pressure, General political/social/cultural problems</t>
+          <t>Economic/status pressure, Men's behavior, Global political/social/cultural problems</t>
         </is>
       </c>
       <c r="Q7" s="3" t="inlineStr"/>
@@ -1337,24 +1337,24 @@
       <c r="S7" s="3" t="inlineStr"/>
       <c r="T7" s="3" t="inlineStr">
         <is>
-          <t>Commentary/opinion, Personal story, News/telling facts</t>
+          <t>Commentary/opinion, News/telling facts, Personal story</t>
         </is>
       </c>
       <c r="U7" s="3" t="inlineStr"/>
       <c r="V7" s="3" t="inlineStr">
         <is>
-          <t>Information seeking, Connection/social interaction, Self expression/identity construction</t>
+          <t>Self expression/identity construction, Connection/social interaction, Information seeking</t>
         </is>
       </c>
       <c r="W7" s="3" t="inlineStr">
         <is>
-          <t>Personal experience, Cultural/social observations, Facts/statistics, Generalizations about men/women</t>
+          <t>Generalizations about men/women, Cultural/social observations, Personal experience, Facts/statistics</t>
         </is>
       </c>
       <c r="X7" s="3" t="inlineStr"/>
       <c r="Y7" s="3" t="inlineStr">
         <is>
-          <t>Anecdotal examples, Presented as common sense, References data</t>
+          <t>Presented as common sense, Anecdotal examples, References data</t>
         </is>
       </c>
       <c r="Z7" s="3" t="inlineStr"/>
@@ -1444,7 +1444,7 @@
       <c r="O8" s="3" t="inlineStr"/>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t>General political/social/cultural problems</t>
+          <t>Global political/social/cultural problems</t>
         </is>
       </c>
       <c r="Q8" s="3" t="inlineStr"/>
@@ -1462,7 +1462,7 @@
       <c r="U8" s="3" t="inlineStr"/>
       <c r="V8" s="3" t="inlineStr">
         <is>
-          <t>Information seeking, Connection/social interaction</t>
+          <t>Connection/social interaction, Information seeking</t>
         </is>
       </c>
       <c r="W8" s="3" t="inlineStr">
@@ -1473,7 +1473,7 @@
       <c r="X8" s="3" t="inlineStr"/>
       <c r="Y8" s="3" t="inlineStr">
         <is>
-          <t>References data, Anecdotal examples, Presented as common sense</t>
+          <t>Presented as common sense, Anecdotal examples, References data</t>
         </is>
       </c>
       <c r="Z8" s="3" t="inlineStr"/>
@@ -1563,7 +1563,7 @@
       <c r="O9" s="3" t="inlineStr"/>
       <c r="P9" s="3" t="inlineStr">
         <is>
-          <t>Men’s behavior</t>
+          <t>Men's behavior</t>
         </is>
       </c>
       <c r="Q9" s="3" t="inlineStr"/>
@@ -1649,7 +1649,7 @@
       <c r="F10" s="3" t="inlineStr"/>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>Gender issues, e.g. equality, Family/children, Friends/socializing</t>
+          <t>Gender issues, e.g. equality, Friends/socializing, Family/children</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr"/>
@@ -1682,7 +1682,7 @@
       <c r="O10" s="3" t="inlineStr"/>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t>General political/social/cultural problems, Men’s behavior</t>
+          <t>Men's behavior, Global political/social/cultural problems</t>
         </is>
       </c>
       <c r="Q10" s="3" t="inlineStr"/>
@@ -1700,12 +1700,12 @@
       <c r="U10" s="3" t="inlineStr"/>
       <c r="V10" s="3" t="inlineStr">
         <is>
-          <t>Entertainment/escapism, Connection/social interaction</t>
+          <t>Connection/social interaction, Entertainment/escapism</t>
         </is>
       </c>
       <c r="W10" s="3" t="inlineStr">
         <is>
-          <t>Cultural/social observations, Generalizations about men/women</t>
+          <t>Generalizations about men/women, Cultural/social observations</t>
         </is>
       </c>
       <c r="X10" s="3" t="inlineStr"/>
@@ -1805,7 +1805,7 @@
       <c r="O11" s="3" t="inlineStr"/>
       <c r="P11" s="3" t="inlineStr">
         <is>
-          <t>Kenyan or Nigerian political/social problems, Men’s behavior</t>
+          <t>Kenyan or Nigerian political/social problems, Men's behavior</t>
         </is>
       </c>
       <c r="Q11" s="3" t="inlineStr"/>
@@ -1823,7 +1823,7 @@
       <c r="U11" s="3" t="inlineStr"/>
       <c r="V11" s="3" t="inlineStr">
         <is>
-          <t>Entertainment/escapism, Connection/social interaction</t>
+          <t>Connection/social interaction, Entertainment/escapism</t>
         </is>
       </c>
       <c r="W11" s="3" t="inlineStr">
@@ -1924,25 +1924,25 @@
       <c r="O12" s="3" t="inlineStr"/>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t>General political/social/cultural problems, Men’s behavior, Women/feminism</t>
+          <t>Women/feminism, Men's behavior, Global political/social/cultural problems</t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr"/>
       <c r="R12" s="3" t="inlineStr">
         <is>
-          <t>More self-discipline/fitness, More equality/respect for men, More equality/respect for women</t>
+          <t>More equality/respect for women, More equality/respect for men, More self-discipline/fitness</t>
         </is>
       </c>
       <c r="S12" s="3" t="inlineStr"/>
       <c r="T12" s="3" t="inlineStr">
         <is>
-          <t>Commentary/opinion, Advice/instruction</t>
+          <t>Advice/instruction, Commentary/opinion</t>
         </is>
       </c>
       <c r="U12" s="3" t="inlineStr"/>
       <c r="V12" s="3" t="inlineStr">
         <is>
-          <t>Entertainment/escapism, Connection/social interaction</t>
+          <t>Connection/social interaction, Entertainment/escapism</t>
         </is>
       </c>
       <c r="W12" s="3" t="inlineStr">
@@ -2043,7 +2043,7 @@
       <c r="O13" s="3" t="inlineStr"/>
       <c r="P13" s="3" t="inlineStr">
         <is>
-          <t>Kenyan or Nigerian political/social problems, Men’s behavior</t>
+          <t>Kenyan or Nigerian political/social problems, Men's behavior</t>
         </is>
       </c>
       <c r="Q13" s="3" t="inlineStr"/>
@@ -2061,7 +2061,7 @@
       <c r="U13" s="3" t="inlineStr"/>
       <c r="V13" s="3" t="inlineStr">
         <is>
-          <t>Entertainment/escapism, Connection/social interaction</t>
+          <t>Connection/social interaction, Entertainment/escapism</t>
         </is>
       </c>
       <c r="W13" s="3" t="inlineStr">
@@ -2129,7 +2129,7 @@
       <c r="F14" s="3" t="inlineStr"/>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>Family/children, Gender issues, e.g. equality, Dating/marriage, Mental health</t>
+          <t>Gender issues, e.g. equality, Dating/marriage, Family/children, Mental health</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr"/>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t>Men need to improve themselves, Men need to be equal partners, Men need to be emotionally open, Other</t>
+          <t>Men need to be emotionally open, Men need to improve themselves, Men need to be equal partners, Other</t>
         </is>
       </c>
       <c r="O14" s="3" t="inlineStr">
@@ -2166,36 +2166,36 @@
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
-          <t>Men’s behavior, Mental health/emotional struggle, General political/social/cultural problems</t>
+          <t>Mental health/emotional struggle, Men's behavior, Global political/social/cultural problems</t>
         </is>
       </c>
       <c r="Q14" s="3" t="inlineStr"/>
       <c r="R14" s="3" t="inlineStr">
         <is>
-          <t>More emotional growth/healing, More equality/respect for women</t>
+          <t>More equality/respect for women, More emotional growth/healing</t>
         </is>
       </c>
       <c r="S14" s="3" t="inlineStr"/>
       <c r="T14" s="3" t="inlineStr">
         <is>
-          <t>Personal story, Commentary/opinion, Advice/instruction</t>
+          <t>Advice/instruction, Commentary/opinion, Personal story</t>
         </is>
       </c>
       <c r="U14" s="3" t="inlineStr"/>
       <c r="V14" s="3" t="inlineStr">
         <is>
-          <t>Information seeking, Connection/social interaction, Self expression/identity construction</t>
+          <t>Self expression/identity construction, Connection/social interaction, Information seeking</t>
         </is>
       </c>
       <c r="W14" s="3" t="inlineStr">
         <is>
-          <t>Generalizations about men/women, Personal experience, Stories about men/women, Cultural/social observations</t>
+          <t>Generalizations about men/women, Cultural/social observations, Stories about men/women, Personal experience</t>
         </is>
       </c>
       <c r="X14" s="3" t="inlineStr"/>
       <c r="Y14" s="3" t="inlineStr">
         <is>
-          <t>Anecdotal examples, Presented as common sense</t>
+          <t>Presented as common sense, Anecdotal examples</t>
         </is>
       </c>
       <c r="Z14" s="3" t="inlineStr"/>
@@ -2252,7 +2252,7 @@
       <c r="F15" s="3" t="inlineStr"/>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>Dating/marriage, Money/status, Gender issues, e.g. equality</t>
+          <t>Gender issues, e.g. equality, Dating/marriage, Money/status</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr"/>
@@ -2285,7 +2285,7 @@
       <c r="O15" s="3" t="inlineStr"/>
       <c r="P15" s="3" t="inlineStr">
         <is>
-          <t>Economic/status pressure, Men’s behavior, General political/social/cultural problems</t>
+          <t>Economic/status pressure, Men's behavior, Global political/social/cultural problems</t>
         </is>
       </c>
       <c r="Q15" s="3" t="inlineStr"/>
@@ -2303,12 +2303,12 @@
       <c r="U15" s="3" t="inlineStr"/>
       <c r="V15" s="3" t="inlineStr">
         <is>
-          <t>Information seeking, Connection/social interaction, Self expression/identity construction</t>
+          <t>Self expression/identity construction, Connection/social interaction, Information seeking</t>
         </is>
       </c>
       <c r="W15" s="3" t="inlineStr">
         <is>
-          <t>Cultural/social observations, Generalizations about men/women</t>
+          <t>Generalizations about men/women, Cultural/social observations</t>
         </is>
       </c>
       <c r="X15" s="3" t="inlineStr"/>
@@ -2371,7 +2371,7 @@
       <c r="F16" s="3" t="inlineStr"/>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>Mental health, Money/status, Family/children, Gender issues, e.g. equality</t>
+          <t>Gender issues, e.g. equality, Family/children, Mental health, Money/status</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr"/>
@@ -2398,13 +2398,13 @@
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t>Men need to provide/succeed, Men need to not show emotions, Men need to be emotionally open</t>
+          <t>Men need to be emotionally open, Men need to not show emotions, Men need to provide/succeed</t>
         </is>
       </c>
       <c r="O16" s="3" t="inlineStr"/>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t>Mental health/emotional struggle, Economic/status pressure, General political/social/cultural problems</t>
+          <t>Mental health/emotional struggle, Economic/status pressure, Global political/social/cultural problems</t>
         </is>
       </c>
       <c r="Q16" s="3" t="inlineStr"/>
@@ -2422,18 +2422,18 @@
       <c r="U16" s="3" t="inlineStr"/>
       <c r="V16" s="3" t="inlineStr">
         <is>
-          <t>Information seeking, Connection/social interaction, Self expression/identity construction</t>
+          <t>Self expression/identity construction, Connection/social interaction, Information seeking</t>
         </is>
       </c>
       <c r="W16" s="3" t="inlineStr">
         <is>
-          <t>Cultural/social observations, Generalizations about men/women, Stories about men/women</t>
+          <t>Generalizations about men/women, Cultural/social observations, Stories about men/women</t>
         </is>
       </c>
       <c r="X16" s="3" t="inlineStr"/>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t>Anecdotal examples, Presented as common sense</t>
+          <t>Presented as common sense, Anecdotal examples</t>
         </is>
       </c>
       <c r="Z16" s="3" t="inlineStr"/>
@@ -2498,7 +2498,7 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>Dating/marriage, Gender issues, e.g. equality, Money/status</t>
+          <t>Gender issues, e.g. equality, Dating/marriage, Money/status</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr"/>
@@ -2525,13 +2525,13 @@
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t>Men need to dominate/lead, Men need to be fully self-reliant</t>
+          <t>Men need to be fully self-reliant, Men need to dominate/lead</t>
         </is>
       </c>
       <c r="O17" s="3" t="inlineStr"/>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t>Women/feminism, Economic/status pressure, Men’s behavior</t>
+          <t>Economic/status pressure, Women/feminism, Men's behavior</t>
         </is>
       </c>
       <c r="Q17" s="3" t="inlineStr"/>
@@ -2553,7 +2553,7 @@
       <c r="U17" s="3" t="inlineStr"/>
       <c r="V17" s="3" t="inlineStr">
         <is>
-          <t>Connection/social interaction, Self expression/identity construction</t>
+          <t>Self expression/identity construction, Connection/social interaction</t>
         </is>
       </c>
       <c r="W17" s="3" t="inlineStr">
@@ -2595,7 +2595,7 @@
       </c>
       <c r="AF17" s="3" t="inlineStr">
         <is>
-          <t>Calls for men to follow more traditional gender norms, Other</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="AG17" s="3" t="inlineStr">
@@ -2633,7 +2633,7 @@
       <c r="F18" s="3" t="inlineStr"/>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>Dating/marriage, Money/status, Gender issues, e.g. equality</t>
+          <t>Gender issues, e.g. equality, Dating/marriage, Money/status</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr"/>
@@ -2660,19 +2660,19 @@
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t>Men need to provide/succeed, Men need to be fully self-reliant, Men need to improve themselves</t>
+          <t>Men need to be fully self-reliant, Men need to improve themselves, Men need to provide/succeed</t>
         </is>
       </c>
       <c r="O18" s="3" t="inlineStr"/>
       <c r="P18" s="3" t="inlineStr">
         <is>
-          <t>Women/feminism, Economic/status pressure, Men’s behavior</t>
+          <t>Economic/status pressure, Women/feminism, Men's behavior</t>
         </is>
       </c>
       <c r="Q18" s="3" t="inlineStr"/>
       <c r="R18" s="3" t="inlineStr">
         <is>
-          <t>More wealth/status, More self-discipline/fitness, Other</t>
+          <t>More self-discipline/fitness, More wealth/status, Other</t>
         </is>
       </c>
       <c r="S18" s="3" t="inlineStr">
@@ -2688,7 +2688,7 @@
       <c r="U18" s="3" t="inlineStr"/>
       <c r="V18" s="3" t="inlineStr">
         <is>
-          <t>Information seeking, Self expression/identity construction, Status seeking</t>
+          <t>Self expression/identity construction, Information seeking, Status seeking</t>
         </is>
       </c>
       <c r="W18" s="3" t="inlineStr">
@@ -2699,7 +2699,7 @@
       <c r="X18" s="3" t="inlineStr"/>
       <c r="Y18" s="3" t="inlineStr">
         <is>
-          <t>No justification, Presented as common sense</t>
+          <t>Presented as common sense, No justification</t>
         </is>
       </c>
       <c r="Z18" s="3" t="inlineStr"/>
@@ -2730,7 +2730,7 @@
       </c>
       <c r="AF18" s="3" t="inlineStr">
         <is>
-          <t>Calls for men to follow more traditional gender norms, Other</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="AG18" s="3" t="inlineStr">
@@ -2764,7 +2764,7 @@
       <c r="F19" s="3" t="inlineStr"/>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>Dating/marriage, Money/status, Family/children, Gender issues, e.g. equality</t>
+          <t>Gender issues, e.g. equality, Dating/marriage, Family/children, Money/status</t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr"/>
@@ -2797,7 +2797,7 @@
       <c r="O19" s="3" t="inlineStr"/>
       <c r="P19" s="3" t="inlineStr">
         <is>
-          <t>General political/social/cultural problems, Men’s behavior, Economic/status pressure</t>
+          <t>Economic/status pressure, Men's behavior, Global political/social/cultural problems</t>
         </is>
       </c>
       <c r="Q19" s="3" t="inlineStr"/>
@@ -2815,7 +2815,7 @@
       <c r="U19" s="3" t="inlineStr"/>
       <c r="V19" s="3" t="inlineStr">
         <is>
-          <t>Information seeking, Connection/social interaction, Self expression/identity construction</t>
+          <t>Self expression/identity construction, Connection/social interaction, Information seeking</t>
         </is>
       </c>
       <c r="W19" s="3" t="inlineStr">
@@ -2826,7 +2826,7 @@
       <c r="X19" s="3" t="inlineStr"/>
       <c r="Y19" s="3" t="inlineStr">
         <is>
-          <t>No justification, Presented as common sense</t>
+          <t>Presented as common sense, No justification</t>
         </is>
       </c>
       <c r="Z19" s="3" t="inlineStr"/>
@@ -2891,7 +2891,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>Dating/marriage, Money/status, Gender issues, e.g. equality</t>
+          <t>Gender issues, e.g. equality, Dating/marriage, Money/status</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr"/>
@@ -2924,7 +2924,7 @@
       <c r="O20" s="3" t="inlineStr"/>
       <c r="P20" s="3" t="inlineStr">
         <is>
-          <t>Economic/status pressure, Women/feminism, General political/social/cultural problems</t>
+          <t>Economic/status pressure, Women/feminism, Global political/social/cultural problems</t>
         </is>
       </c>
       <c r="Q20" s="3" t="inlineStr"/>
@@ -2946,7 +2946,7 @@
       <c r="U20" s="3" t="inlineStr"/>
       <c r="V20" s="3" t="inlineStr">
         <is>
-          <t>Connection/social interaction, Self expression/identity construction, Status seeking</t>
+          <t>Self expression/identity construction, Connection/social interaction, Status seeking</t>
         </is>
       </c>
       <c r="W20" s="3" t="inlineStr">
@@ -2957,7 +2957,7 @@
       <c r="X20" s="3" t="inlineStr"/>
       <c r="Y20" s="3" t="inlineStr">
         <is>
-          <t>No justification, Anecdotal examples, Presented as common sense</t>
+          <t>Presented as common sense, Anecdotal examples, No justification</t>
         </is>
       </c>
       <c r="Z20" s="3" t="inlineStr"/>
@@ -3014,7 +3014,7 @@
       <c r="F21" s="3" t="inlineStr"/>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>Dating/marriage, Money/status, Fitness/self-improvement</t>
+          <t>Fitness/self-improvement, Dating/marriage, Money/status</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr"/>
@@ -3051,13 +3051,13 @@
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
-          <t>Men’s behavior, Economic/status pressure, Women/feminism</t>
+          <t>Economic/status pressure, Women/feminism, Men's behavior</t>
         </is>
       </c>
       <c r="Q21" s="3" t="inlineStr"/>
       <c r="R21" s="3" t="inlineStr">
         <is>
-          <t>More wealth/status, More self-discipline/fitness</t>
+          <t>More self-discipline/fitness, More wealth/status</t>
         </is>
       </c>
       <c r="S21" s="3" t="inlineStr"/>
@@ -3069,7 +3069,7 @@
       <c r="U21" s="3" t="inlineStr"/>
       <c r="V21" s="3" t="inlineStr">
         <is>
-          <t>Information seeking, Self expression/identity construction, Status seeking</t>
+          <t>Self expression/identity construction, Information seeking, Status seeking</t>
         </is>
       </c>
       <c r="W21" s="3" t="inlineStr">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="AF21" s="3" t="inlineStr">
         <is>
-          <t>Calls for men to follow more traditional gender norms, Other</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="AG21" s="3" t="inlineStr">
@@ -3176,13 +3176,13 @@
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
-          <t>Men need to provide/succeed, Men need to improve themselves, Men need to be fully self-reliant</t>
+          <t>Men need to be fully self-reliant, Men need to improve themselves, Men need to provide/succeed</t>
         </is>
       </c>
       <c r="O22" s="3" t="inlineStr"/>
       <c r="P22" s="3" t="inlineStr">
         <is>
-          <t>General political/social/cultural problems, Women/feminism, Men’s behavior, Economic/status pressure</t>
+          <t>Economic/status pressure, Women/feminism, Men's behavior, Global political/social/cultural problems</t>
         </is>
       </c>
       <c r="Q22" s="3" t="inlineStr"/>
@@ -3200,7 +3200,7 @@
       <c r="U22" s="3" t="inlineStr"/>
       <c r="V22" s="3" t="inlineStr">
         <is>
-          <t>Information seeking, Connection/social interaction, Self expression/identity construction</t>
+          <t>Self expression/identity construction, Connection/social interaction, Information seeking</t>
         </is>
       </c>
       <c r="W22" s="3" t="inlineStr">
@@ -3305,7 +3305,7 @@
       <c r="O23" s="3" t="inlineStr"/>
       <c r="P23" s="3" t="inlineStr">
         <is>
-          <t>Women/feminism, Economic/status pressure, Men’s behavior</t>
+          <t>Economic/status pressure, Women/feminism, Men's behavior</t>
         </is>
       </c>
       <c r="Q23" s="3" t="inlineStr"/>
@@ -3323,7 +3323,7 @@
       <c r="U23" s="3" t="inlineStr"/>
       <c r="V23" s="3" t="inlineStr">
         <is>
-          <t>Information seeking, Connection/social interaction</t>
+          <t>Connection/social interaction, Information seeking</t>
         </is>
       </c>
       <c r="W23" s="3" t="inlineStr">
@@ -3461,7 +3461,7 @@
       <c r="X24" s="3" t="inlineStr"/>
       <c r="Y24" s="3" t="inlineStr">
         <is>
-          <t>No justification, Presented as common sense</t>
+          <t>Presented as common sense, No justification</t>
         </is>
       </c>
       <c r="Z24" s="3" t="inlineStr"/>
@@ -3524,13 +3524,13 @@
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>Compelling question, Shares something surprising</t>
+          <t>Shares something surprising, Compelling question</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr"/>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>Dating/marriage, Money/status, Gender issues, e.g. equality, Religion/morality</t>
+          <t>Gender issues, e.g. equality, Religion/morality, Dating/marriage, Money/status</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr"/>
@@ -3563,7 +3563,7 @@
       <c r="O25" s="3" t="inlineStr"/>
       <c r="P25" s="3" t="inlineStr">
         <is>
-          <t>Kenyan or Nigerian political/social problems, General political/social/cultural problems, Women/feminism, Economic/status pressure</t>
+          <t>Kenyan or Nigerian political/social problems, Economic/status pressure, Women/feminism, Global political/social/cultural problems</t>
         </is>
       </c>
       <c r="Q25" s="3" t="inlineStr"/>
@@ -3575,13 +3575,13 @@
       <c r="S25" s="3" t="inlineStr"/>
       <c r="T25" s="3" t="inlineStr">
         <is>
-          <t>Humor/satire, Commentary/opinion, Debate/argument</t>
+          <t>Commentary/opinion, Debate/argument, Humor/satire</t>
         </is>
       </c>
       <c r="U25" s="3" t="inlineStr"/>
       <c r="V25" s="3" t="inlineStr">
         <is>
-          <t>Entertainment/escapism, Status seeking, Connection/social interaction, Self expression/identity construction</t>
+          <t>Self expression/identity construction, Connection/social interaction, Entertainment/escapism, Status seeking</t>
         </is>
       </c>
       <c r="W25" s="3" t="inlineStr">
@@ -3592,7 +3592,7 @@
       <c r="X25" s="3" t="inlineStr"/>
       <c r="Y25" s="3" t="inlineStr">
         <is>
-          <t>No justification, Presented as common sense</t>
+          <t>Presented as common sense, No justification</t>
         </is>
       </c>
       <c r="Z25" s="3" t="inlineStr"/>
@@ -3692,7 +3692,7 @@
       </c>
       <c r="R26" s="3" t="inlineStr">
         <is>
-          <t>No clear solution, Building community, Other</t>
+          <t>Building community, No clear solution, Other</t>
         </is>
       </c>
       <c r="S26" s="3" t="inlineStr">
@@ -3919,7 +3919,7 @@
       <c r="F28" s="3" t="inlineStr"/>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>Dating/marriage, Gender issues, e.g. equality, Religion/morality, Family/children</t>
+          <t>Gender issues, e.g. equality, Religion/morality, Dating/marriage, Family/children</t>
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr"/>
@@ -3946,7 +3946,7 @@
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
-          <t>Men need to dominate/lead, Men need to provide/succeed, Men need to improve themselves, Other</t>
+          <t>Men need to improve themselves, Men need to provide/succeed, Men need to dominate/lead, Other</t>
         </is>
       </c>
       <c r="O28" s="3" t="inlineStr">
@@ -3956,7 +3956,7 @@
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
-          <t>General political/social/cultural problems, Men’s behavior</t>
+          <t>Men's behavior, Global political/social/cultural problems</t>
         </is>
       </c>
       <c r="Q28" s="3" t="inlineStr"/>
@@ -3972,18 +3972,18 @@
       </c>
       <c r="T28" s="3" t="inlineStr">
         <is>
-          <t>Advice/instruction, Commentary/opinion, Motivational speech</t>
+          <t>Motivational speech, Advice/instruction, Commentary/opinion</t>
         </is>
       </c>
       <c r="U28" s="3" t="inlineStr"/>
       <c r="V28" s="3" t="inlineStr">
         <is>
-          <t>Information seeking, Connection/social interaction, Self expression/identity construction</t>
+          <t>Self expression/identity construction, Connection/social interaction, Information seeking</t>
         </is>
       </c>
       <c r="W28" s="3" t="inlineStr">
         <is>
-          <t>Moral/religious claims, Cultural/social observations, Generalizations about men/women</t>
+          <t>Generalizations about men/women, Cultural/social observations, Moral/religious claims</t>
         </is>
       </c>
       <c r="X28" s="3" t="inlineStr"/>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="AF28" s="3" t="inlineStr">
         <is>
-          <t>Calls for men to follow more traditional gender norms, Other</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="AG28" s="3" t="inlineStr">
@@ -4052,13 +4052,13 @@
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>Interesting visual or meme, Shares something sexual, Shares something surprising</t>
+          <t>Shares something surprising, Interesting visual or meme, Shares something sexual</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr"/>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>Dating/marriage, Gender issues, e.g. equality, Other</t>
+          <t>Gender issues, e.g. equality, Dating/marriage, Other</t>
         </is>
       </c>
       <c r="H29" s="3" t="inlineStr">
@@ -4089,7 +4089,7 @@
       </c>
       <c r="N29" s="3" t="inlineStr">
         <is>
-          <t>Men need to dominate/lead, Men are disadvantaged/victims, Other</t>
+          <t>Men are disadvantaged/victims, Men need to dominate/lead, Other</t>
         </is>
       </c>
       <c r="O29" s="3" t="inlineStr">
@@ -4099,7 +4099,7 @@
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
-          <t>Women/feminism, General political/social/cultural problems, Men’s behavior, Other</t>
+          <t>Women/feminism, Men's behavior, Other, Global political/social/cultural problems</t>
         </is>
       </c>
       <c r="Q29" s="3" t="inlineStr">
@@ -4119,24 +4119,24 @@
       </c>
       <c r="T29" s="3" t="inlineStr">
         <is>
-          <t>Commentary/opinion, Advice/instruction</t>
+          <t>Advice/instruction, Commentary/opinion</t>
         </is>
       </c>
       <c r="U29" s="3" t="inlineStr"/>
       <c r="V29" s="3" t="inlineStr">
         <is>
-          <t>Entertainment/escapism, Connection/social interaction, Self expression/identity construction</t>
+          <t>Self expression/identity construction, Connection/social interaction, Entertainment/escapism</t>
         </is>
       </c>
       <c r="W29" s="3" t="inlineStr">
         <is>
-          <t>Stories about men/women, Generalizations about men/women, No support</t>
+          <t>Generalizations about men/women, Stories about men/women, No support</t>
         </is>
       </c>
       <c r="X29" s="3" t="inlineStr"/>
       <c r="Y29" s="3" t="inlineStr">
         <is>
-          <t>No justification, Anecdotal examples, Presented as common sense</t>
+          <t>Presented as common sense, Anecdotal examples, No justification</t>
         </is>
       </c>
       <c r="Z29" s="3" t="inlineStr"/>
@@ -4226,7 +4226,7 @@
       <c r="O30" s="3" t="inlineStr"/>
       <c r="P30" s="3" t="inlineStr">
         <is>
-          <t>Women/feminism, Mental health/emotional struggle, Men’s behavior</t>
+          <t>Mental health/emotional struggle, Women/feminism, Men's behavior</t>
         </is>
       </c>
       <c r="Q30" s="3" t="inlineStr"/>
@@ -4248,7 +4248,7 @@
       <c r="U30" s="3" t="inlineStr"/>
       <c r="V30" s="3" t="inlineStr">
         <is>
-          <t>Connection/social interaction, Self expression/identity construction</t>
+          <t>Self expression/identity construction, Connection/social interaction</t>
         </is>
       </c>
       <c r="W30" s="3" t="inlineStr">
@@ -4259,7 +4259,7 @@
       <c r="X30" s="3" t="inlineStr"/>
       <c r="Y30" s="3" t="inlineStr">
         <is>
-          <t>Anecdotal examples, Presented as common sense</t>
+          <t>Presented as common sense, Anecdotal examples</t>
         </is>
       </c>
       <c r="Z30" s="3" t="inlineStr"/>
@@ -4347,13 +4347,13 @@
       </c>
       <c r="N31" s="3" t="inlineStr">
         <is>
-          <t>Men need to dominate/lead, Men need to provide/succeed</t>
+          <t>Men need to provide/succeed, Men need to dominate/lead</t>
         </is>
       </c>
       <c r="O31" s="3" t="inlineStr"/>
       <c r="P31" s="3" t="inlineStr">
         <is>
-          <t>Economic/status pressure, Men’s behavior, General political/social/cultural problems</t>
+          <t>Economic/status pressure, Men's behavior, Global political/social/cultural problems</t>
         </is>
       </c>
       <c r="Q31" s="3" t="inlineStr"/>
@@ -4369,13 +4369,13 @@
       </c>
       <c r="T31" s="3" t="inlineStr">
         <is>
-          <t>Personal story, Commentary/opinion</t>
+          <t>Commentary/opinion, Personal story</t>
         </is>
       </c>
       <c r="U31" s="3" t="inlineStr"/>
       <c r="V31" s="3" t="inlineStr">
         <is>
-          <t>Connection/social interaction, Self expression/identity construction, Status seeking</t>
+          <t>Self expression/identity construction, Connection/social interaction, Status seeking</t>
         </is>
       </c>
       <c r="W31" s="3" t="inlineStr">
@@ -4386,7 +4386,7 @@
       <c r="X31" s="3" t="inlineStr"/>
       <c r="Y31" s="3" t="inlineStr">
         <is>
-          <t>Anecdotal examples, Presented as common sense</t>
+          <t>Presented as common sense, Anecdotal examples</t>
         </is>
       </c>
       <c r="Z31" s="3" t="inlineStr"/>
@@ -4443,7 +4443,7 @@
       <c r="F32" s="3" t="inlineStr"/>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>Dating/marriage, Gender issues, e.g. equality, Friends/socializing, Other</t>
+          <t>Gender issues, e.g. equality, Friends/socializing, Dating/marriage, Other</t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr">
@@ -4480,7 +4480,7 @@
       <c r="O32" s="3" t="inlineStr"/>
       <c r="P32" s="3" t="inlineStr">
         <is>
-          <t>Men’s behavior, Women/feminism, General political/social/cultural problems</t>
+          <t>Women/feminism, Men's behavior, Global political/social/cultural problems</t>
         </is>
       </c>
       <c r="Q32" s="3" t="inlineStr"/>
@@ -4498,18 +4498,18 @@
       <c r="U32" s="3" t="inlineStr"/>
       <c r="V32" s="3" t="inlineStr">
         <is>
-          <t>Connection/social interaction, Information seeking, Self expression/identity construction</t>
+          <t>Self expression/identity construction, Connection/social interaction, Information seeking</t>
         </is>
       </c>
       <c r="W32" s="3" t="inlineStr">
         <is>
-          <t>Cultural/social observations, Generalizations about men/women, Facts/statistics</t>
+          <t>Generalizations about men/women, Cultural/social observations, Facts/statistics</t>
         </is>
       </c>
       <c r="X32" s="3" t="inlineStr"/>
       <c r="Y32" s="3" t="inlineStr">
         <is>
-          <t>Anecdotal examples, Presented as common sense, References data</t>
+          <t>Presented as common sense, Anecdotal examples, References data</t>
         </is>
       </c>
       <c r="Z32" s="3" t="inlineStr"/>
@@ -4570,7 +4570,7 @@
       <c r="F33" s="3" t="inlineStr"/>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>Dating/marriage, Gender issues, e.g. equality, Friends/socializing</t>
+          <t>Gender issues, e.g. equality, Friends/socializing, Dating/marriage</t>
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr"/>
@@ -4603,7 +4603,7 @@
       <c r="O33" s="3" t="inlineStr"/>
       <c r="P33" s="3" t="inlineStr">
         <is>
-          <t>Women/feminism, Men’s behavior, General political/social/cultural problems</t>
+          <t>Women/feminism, Men's behavior, Global political/social/cultural problems</t>
         </is>
       </c>
       <c r="Q33" s="3" t="inlineStr"/>
@@ -4621,7 +4621,7 @@
       <c r="U33" s="3" t="inlineStr"/>
       <c r="V33" s="3" t="inlineStr">
         <is>
-          <t>Information seeking, Connection/social interaction, Self expression/identity construction</t>
+          <t>Self expression/identity construction, Connection/social interaction, Information seeking</t>
         </is>
       </c>
       <c r="W33" s="3" t="inlineStr">
@@ -4632,7 +4632,7 @@
       <c r="X33" s="3" t="inlineStr"/>
       <c r="Y33" s="3" t="inlineStr">
         <is>
-          <t>Anecdotal examples, Presented as common sense, No justification</t>
+          <t>Presented as common sense, Anecdotal examples, No justification</t>
         </is>
       </c>
       <c r="Z33" s="3" t="inlineStr"/>
@@ -4705,7 +4705,7 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>Family/children, Religion/morality, Gender issues, e.g. equality, Other</t>
+          <t>Gender issues, e.g. equality, Religion/morality, Family/children, Other</t>
         </is>
       </c>
       <c r="H34" s="3" t="inlineStr">
@@ -4742,7 +4742,7 @@
       <c r="O34" s="3" t="inlineStr"/>
       <c r="P34" s="3" t="inlineStr">
         <is>
-          <t>General political/social/cultural problems, Women/feminism, Other</t>
+          <t>Women/feminism, Other, Global political/social/cultural problems</t>
         </is>
       </c>
       <c r="Q34" s="3" t="inlineStr">
@@ -4764,12 +4764,12 @@
       <c r="U34" s="3" t="inlineStr"/>
       <c r="V34" s="3" t="inlineStr">
         <is>
-          <t>Information seeking, Self expression/identity construction</t>
+          <t>Self expression/identity construction, Information seeking</t>
         </is>
       </c>
       <c r="W34" s="3" t="inlineStr">
         <is>
-          <t>Generalizations about men/women, Moral/religious claims, Cultural/social observations, No support</t>
+          <t>Generalizations about men/women, Cultural/social observations, Moral/religious claims, No support</t>
         </is>
       </c>
       <c r="X34" s="3" t="inlineStr"/>
@@ -4806,7 +4806,7 @@
       </c>
       <c r="AF34" s="3" t="inlineStr">
         <is>
-          <t>Calls for women to follow more traditional gender norms</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="AG34" s="3" t="inlineStr"/>
@@ -4840,7 +4840,7 @@
       <c r="F35" s="3" t="inlineStr"/>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>Dating/marriage, Gender issues, e.g. equality</t>
+          <t>Gender issues, e.g. equality, Dating/marriage</t>
         </is>
       </c>
       <c r="H35" s="3" t="inlineStr"/>
@@ -4873,7 +4873,7 @@
       <c r="O35" s="3" t="inlineStr"/>
       <c r="P35" s="3" t="inlineStr">
         <is>
-          <t>Women/feminism, General political/social/cultural problems, Men’s behavior</t>
+          <t>Women/feminism, Men's behavior, Global political/social/cultural problems</t>
         </is>
       </c>
       <c r="Q35" s="3" t="inlineStr"/>
@@ -4963,7 +4963,7 @@
       <c r="F36" s="3" t="inlineStr"/>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>Family/children, Religion/morality</t>
+          <t>Religion/morality, Family/children</t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr"/>
@@ -4996,7 +4996,7 @@
       <c r="O36" s="3" t="inlineStr"/>
       <c r="P36" s="3" t="inlineStr">
         <is>
-          <t>General political/social/cultural problems, Other</t>
+          <t>Other, Global political/social/cultural problems</t>
         </is>
       </c>
       <c r="Q36" s="3" t="inlineStr">
@@ -5012,18 +5012,18 @@
       <c r="S36" s="3" t="inlineStr"/>
       <c r="T36" s="3" t="inlineStr">
         <is>
-          <t>Personal story, Commentary/opinion</t>
+          <t>Commentary/opinion, Personal story</t>
         </is>
       </c>
       <c r="U36" s="3" t="inlineStr"/>
       <c r="V36" s="3" t="inlineStr">
         <is>
-          <t>Information seeking, Self expression/identity construction</t>
+          <t>Self expression/identity construction, Information seeking</t>
         </is>
       </c>
       <c r="W36" s="3" t="inlineStr">
         <is>
-          <t>Personal experience, Cultural/social observations, Moral/religious claims</t>
+          <t>Cultural/social observations, Moral/religious claims, Personal experience</t>
         </is>
       </c>
       <c r="X36" s="3" t="inlineStr"/>
@@ -5086,7 +5086,7 @@
       <c r="F37" s="3" t="inlineStr"/>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>Dating/marriage, Gender issues, e.g. equality, Family/children</t>
+          <t>Gender issues, e.g. equality, Dating/marriage, Family/children</t>
         </is>
       </c>
       <c r="H37" s="3" t="inlineStr"/>
@@ -5119,7 +5119,7 @@
       <c r="O37" s="3" t="inlineStr"/>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t>Women/feminism, General political/social/cultural problems, Men’s behavior</t>
+          <t>Women/feminism, Men's behavior, Global political/social/cultural problems</t>
         </is>
       </c>
       <c r="Q37" s="3" t="inlineStr"/>
@@ -5137,7 +5137,7 @@
       <c r="U37" s="3" t="inlineStr"/>
       <c r="V37" s="3" t="inlineStr">
         <is>
-          <t>Information seeking, Connection/social interaction</t>
+          <t>Connection/social interaction, Information seeking</t>
         </is>
       </c>
       <c r="W37" s="3" t="inlineStr">
@@ -5148,7 +5148,7 @@
       <c r="X37" s="3" t="inlineStr"/>
       <c r="Y37" s="3" t="inlineStr">
         <is>
-          <t>Anecdotal examples, Presented as common sense</t>
+          <t>Presented as common sense, Anecdotal examples, /</t>
         </is>
       </c>
       <c r="Z37" s="3" t="inlineStr"/>
@@ -5209,7 +5209,7 @@
       <c r="F38" s="3" t="inlineStr"/>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>Dating/marriage, Family/children, Gender issues, e.g. equality</t>
+          <t>Gender issues, e.g. equality, Dating/marriage, Family/children</t>
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr"/>
@@ -5254,13 +5254,13 @@
       <c r="S38" s="3" t="inlineStr"/>
       <c r="T38" s="3" t="inlineStr">
         <is>
-          <t>Debate/argument, Commentary/opinion</t>
+          <t>Commentary/opinion, Debate/argument</t>
         </is>
       </c>
       <c r="U38" s="3" t="inlineStr"/>
       <c r="V38" s="3" t="inlineStr">
         <is>
-          <t>Information seeking, Connection/social interaction</t>
+          <t>Connection/social interaction, Information seeking</t>
         </is>
       </c>
       <c r="W38" s="3" t="inlineStr">
@@ -5355,13 +5355,13 @@
       </c>
       <c r="N39" s="3" t="inlineStr">
         <is>
-          <t>Men need to improve themselves, Men need to be emotionally open, Men need to be equal partners</t>
+          <t>Men need to be emotionally open, Men need to improve themselves, Men need to be equal partners</t>
         </is>
       </c>
       <c r="O39" s="3" t="inlineStr"/>
       <c r="P39" s="3" t="inlineStr">
         <is>
-          <t>Men’s behavior, General political/social/cultural problems</t>
+          <t>Men's behavior, Global political/social/cultural problems</t>
         </is>
       </c>
       <c r="Q39" s="3" t="inlineStr"/>
@@ -5377,24 +5377,24 @@
       </c>
       <c r="T39" s="3" t="inlineStr">
         <is>
-          <t>Personal story, Commentary/opinion</t>
+          <t>Commentary/opinion, Personal story</t>
         </is>
       </c>
       <c r="U39" s="3" t="inlineStr"/>
       <c r="V39" s="3" t="inlineStr">
         <is>
-          <t>Information seeking, Self expression/identity construction</t>
+          <t>Self expression/identity construction, Information seeking</t>
         </is>
       </c>
       <c r="W39" s="3" t="inlineStr">
         <is>
-          <t>Personal experience, Cultural/social observations</t>
+          <t>Cultural/social observations, Personal experience</t>
         </is>
       </c>
       <c r="X39" s="3" t="inlineStr"/>
       <c r="Y39" s="3" t="inlineStr">
         <is>
-          <t>Anecdotal examples, Presented as common sense</t>
+          <t>Presented as common sense, Anecdotal examples</t>
         </is>
       </c>
       <c r="Z39" s="3" t="inlineStr"/>
@@ -5525,7 +5525,7 @@
       <c r="X40" s="3" t="inlineStr"/>
       <c r="Y40" s="3" t="inlineStr">
         <is>
-          <t>No justification, Presented as common sense</t>
+          <t>Presented as common sense, No justification</t>
         </is>
       </c>
       <c r="Z40" s="3" t="inlineStr"/>
@@ -5556,7 +5556,7 @@
       </c>
       <c r="AF40" s="3" t="inlineStr">
         <is>
-          <t>Calls for men to follow more equitable gender norms, Other</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="AG40" s="3" t="inlineStr">
@@ -5590,7 +5590,7 @@
       <c r="F41" s="3" t="inlineStr"/>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>Family/children, Dating/marriage, Money/status, Gender issues, e.g. equality</t>
+          <t>Gender issues, e.g. equality, Dating/marriage, Family/children, Money/status</t>
         </is>
       </c>
       <c r="H41" s="3" t="inlineStr"/>
@@ -5617,13 +5617,13 @@
       </c>
       <c r="N41" s="3" t="inlineStr">
         <is>
-          <t>Men need to provide/succeed, Men need to be equal partners, Mixed/unclear</t>
+          <t>Men need to be equal partners, Men need to provide/succeed, Mixed/unclear</t>
         </is>
       </c>
       <c r="O41" s="3" t="inlineStr"/>
       <c r="P41" s="3" t="inlineStr">
         <is>
-          <t>General political/social/cultural problems, Women/feminism, Other</t>
+          <t>Women/feminism, Other, Global political/social/cultural problems</t>
         </is>
       </c>
       <c r="Q41" s="3" t="inlineStr">
@@ -5639,24 +5639,24 @@
       <c r="S41" s="3" t="inlineStr"/>
       <c r="T41" s="3" t="inlineStr">
         <is>
-          <t>Personal story, Commentary/opinion</t>
+          <t>Commentary/opinion, Personal story</t>
         </is>
       </c>
       <c r="U41" s="3" t="inlineStr"/>
       <c r="V41" s="3" t="inlineStr">
         <is>
-          <t>Information seeking, Self expression/identity construction</t>
+          <t>Self expression/identity construction, Information seeking</t>
         </is>
       </c>
       <c r="W41" s="3" t="inlineStr">
         <is>
-          <t>Personal experience, Stories about men/women, Cultural/social observations</t>
+          <t>Cultural/social observations, Stories about men/women, Personal experience</t>
         </is>
       </c>
       <c r="X41" s="3" t="inlineStr"/>
       <c r="Y41" s="3" t="inlineStr">
         <is>
-          <t>Anecdotal examples, References religion/tradition, Presented as common sense</t>
+          <t>References religion/tradition, Presented as common sense, Anecdotal examples</t>
         </is>
       </c>
       <c r="Z41" s="3" t="inlineStr"/>
@@ -5929,7 +5929,7 @@
       <c r="F2" s="3" t="inlineStr"/>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>Money/status, Mental health, Family/children</t>
+          <t>Family/children, Mental health, Money/status</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr"/>
@@ -5962,7 +5962,7 @@
       <c r="O2" s="3" t="inlineStr"/>
       <c r="P2" s="3" t="inlineStr">
         <is>
-          <t>Economic/status pressure, Mental health/emotional struggle</t>
+          <t>Mental health/emotional struggle, Economic/status pressure</t>
         </is>
       </c>
       <c r="Q2" s="3" t="inlineStr"/>
@@ -5980,7 +5980,7 @@
       <c r="U2" s="3" t="inlineStr"/>
       <c r="V2" s="3" t="inlineStr">
         <is>
-          <t>Connection/social interaction, Self expression/identity construction</t>
+          <t>Self expression/identity construction, Connection/social interaction</t>
         </is>
       </c>
       <c r="W2" s="3" t="inlineStr">
@@ -6048,7 +6048,7 @@
       <c r="F3" s="3" t="inlineStr"/>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>Mental health, Gender issues, e.g. equality, Friends/socializing</t>
+          <t>Gender issues, e.g. equality, Friends/socializing, Mental health</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr"/>
@@ -6081,7 +6081,7 @@
       <c r="O3" s="3" t="inlineStr"/>
       <c r="P3" s="3" t="inlineStr">
         <is>
-          <t>Mental health/emotional struggle, Men’s behavior, General political/social/cultural problems, Kenyan or Nigerian political/social problems</t>
+          <t>Kenyan or Nigerian political/social problems, Mental health/emotional struggle, Men's behavior, Global political/social/cultural problems</t>
         </is>
       </c>
       <c r="Q3" s="3" t="inlineStr"/>
@@ -6099,18 +6099,18 @@
       <c r="U3" s="3" t="inlineStr"/>
       <c r="V3" s="3" t="inlineStr">
         <is>
-          <t>Information seeking, Connection/social interaction, Self expression/identity construction</t>
+          <t>Self expression/identity construction, Connection/social interaction, Information seeking</t>
         </is>
       </c>
       <c r="W3" s="3" t="inlineStr">
         <is>
-          <t>Cultural/social observations, Generalizations about men/women</t>
+          <t>Generalizations about men/women, Cultural/social observations</t>
         </is>
       </c>
       <c r="X3" s="3" t="inlineStr"/>
       <c r="Y3" s="3" t="inlineStr">
         <is>
-          <t>Anecdotal examples, Presented as common sense</t>
+          <t>Presented as common sense, Anecdotal examples</t>
         </is>
       </c>
       <c r="Z3" s="3" t="inlineStr"/>
@@ -6167,7 +6167,7 @@
       <c r="F4" s="3" t="inlineStr"/>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Mental health, Gender issues, e.g. equality</t>
+          <t>Gender issues, e.g. equality, Mental health</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr"/>
@@ -6200,7 +6200,7 @@
       <c r="O4" s="3" t="inlineStr"/>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t>Mental health/emotional struggle, General political/social/cultural problems</t>
+          <t>Mental health/emotional struggle, Global political/social/cultural problems</t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr"/>
@@ -6218,12 +6218,12 @@
       <c r="U4" s="3" t="inlineStr"/>
       <c r="V4" s="3" t="inlineStr">
         <is>
-          <t>Information seeking, Connection/social interaction, Self expression/identity construction</t>
+          <t>Self expression/identity construction, Connection/social interaction, Information seeking</t>
         </is>
       </c>
       <c r="W4" s="3" t="inlineStr">
         <is>
-          <t>Cultural/social observations, Generalizations about men/women</t>
+          <t>Generalizations about men/women, Cultural/social observations</t>
         </is>
       </c>
       <c r="X4" s="3" t="inlineStr"/>
@@ -6286,7 +6286,7 @@
       <c r="F5" s="3" t="inlineStr"/>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>Friends/socializing, Mental health, Gender issues, e.g. equality</t>
+          <t>Gender issues, e.g. equality, Friends/socializing, Mental health</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr"/>
@@ -6319,7 +6319,7 @@
       <c r="O5" s="3" t="inlineStr"/>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t>Mental health/emotional struggle, Men’s behavior</t>
+          <t>Mental health/emotional struggle, Men's behavior</t>
         </is>
       </c>
       <c r="Q5" s="3" t="inlineStr"/>
@@ -6331,24 +6331,24 @@
       <c r="S5" s="3" t="inlineStr"/>
       <c r="T5" s="3" t="inlineStr">
         <is>
-          <t>Personal story, Commentary/opinion</t>
+          <t>Commentary/opinion, Personal story</t>
         </is>
       </c>
       <c r="U5" s="3" t="inlineStr"/>
       <c r="V5" s="3" t="inlineStr">
         <is>
-          <t>Information seeking, Connection/social interaction, Self expression/identity construction</t>
+          <t>Self expression/identity construction, Connection/social interaction, Information seeking</t>
         </is>
       </c>
       <c r="W5" s="3" t="inlineStr">
         <is>
-          <t>Personal experience, Cultural/social observations</t>
+          <t>Cultural/social observations, Personal experience</t>
         </is>
       </c>
       <c r="X5" s="3" t="inlineStr"/>
       <c r="Y5" s="3" t="inlineStr">
         <is>
-          <t>Anecdotal examples, Presented as common sense</t>
+          <t>Presented as common sense, Anecdotal examples</t>
         </is>
       </c>
       <c r="Z5" s="3" t="inlineStr"/>
@@ -6405,7 +6405,7 @@
       <c r="F6" s="3" t="inlineStr"/>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>Friends/socializing, Mental health, Gender issues, e.g. equality</t>
+          <t>Gender issues, e.g. equality, Friends/socializing, Mental health</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr"/>
@@ -6442,36 +6442,36 @@
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
-          <t>Men’s behavior, Mental health/emotional struggle, Kenyan or Nigerian political/social problems</t>
+          <t>Kenyan or Nigerian political/social problems, Mental health/emotional struggle, Men's behavior</t>
         </is>
       </c>
       <c r="Q6" s="3" t="inlineStr"/>
       <c r="R6" s="3" t="inlineStr">
         <is>
-          <t>Building community, More emotional growth/healing</t>
+          <t>More emotional growth/healing, Building community</t>
         </is>
       </c>
       <c r="S6" s="3" t="inlineStr"/>
       <c r="T6" s="3" t="inlineStr">
         <is>
-          <t>Personal story, Commentary/opinion</t>
+          <t>Commentary/opinion, Personal story</t>
         </is>
       </c>
       <c r="U6" s="3" t="inlineStr"/>
       <c r="V6" s="3" t="inlineStr">
         <is>
-          <t>Information seeking, Connection/social interaction, Self expression/identity construction</t>
+          <t>Self expression/identity construction, Connection/social interaction, Information seeking</t>
         </is>
       </c>
       <c r="W6" s="3" t="inlineStr">
         <is>
-          <t>Personal experience, Cultural/social observations</t>
+          <t>Cultural/social observations, Personal experience</t>
         </is>
       </c>
       <c r="X6" s="3" t="inlineStr"/>
       <c r="Y6" s="3" t="inlineStr">
         <is>
-          <t>Anecdotal examples, Presented as common sense</t>
+          <t>Presented as common sense, Anecdotal examples</t>
         </is>
       </c>
       <c r="Z6" s="3" t="inlineStr"/>
@@ -6542,7 +6542,7 @@
       <c r="H7" s="3" t="inlineStr"/>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>Interview/conversational content, Motivational/self-help content</t>
+          <t>Interview/conversational content, Motivational/self-help content, /</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr"/>
@@ -6587,7 +6587,7 @@
       <c r="U7" s="3" t="inlineStr"/>
       <c r="V7" s="3" t="inlineStr">
         <is>
-          <t>Information seeking, Connection/social interaction, Self expression/identity construction</t>
+          <t>Self expression/identity construction, Connection/social interaction, Information seeking</t>
         </is>
       </c>
       <c r="W7" s="3" t="inlineStr">
@@ -6663,7 +6663,7 @@
       <c r="F8" s="3" t="inlineStr"/>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>Gender issues, e.g. equality, Mental health, Dating/marriage</t>
+          <t>Gender issues, e.g. equality, Dating/marriage, Mental health</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr"/>
@@ -6696,13 +6696,13 @@
       <c r="O8" s="3" t="inlineStr"/>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t>Mental health/emotional struggle, Women/feminism, Men’s behavior</t>
+          <t>Mental health/emotional struggle, Women/feminism, Men's behavior</t>
         </is>
       </c>
       <c r="Q8" s="3" t="inlineStr"/>
       <c r="R8" s="3" t="inlineStr">
         <is>
-          <t>More emotional growth/healing, More equality/respect for women</t>
+          <t>More equality/respect for women, More emotional growth/healing</t>
         </is>
       </c>
       <c r="S8" s="3" t="inlineStr"/>
@@ -6714,7 +6714,7 @@
       <c r="U8" s="3" t="inlineStr"/>
       <c r="V8" s="3" t="inlineStr">
         <is>
-          <t>Information seeking, Connection/social interaction, Self expression/identity construction</t>
+          <t>Self expression/identity construction, Connection/social interaction, Information seeking</t>
         </is>
       </c>
       <c r="W8" s="3" t="inlineStr">
@@ -6725,7 +6725,7 @@
       <c r="X8" s="3" t="inlineStr"/>
       <c r="Y8" s="3" t="inlineStr">
         <is>
-          <t>Anecdotal examples, Presented as common sense</t>
+          <t>Presented as common sense, Anecdotal examples</t>
         </is>
       </c>
       <c r="Z8" s="3" t="inlineStr"/>
@@ -6782,7 +6782,7 @@
       <c r="F9" s="3" t="inlineStr"/>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>Family/children, Mental health, Social issues, e.g. corruption</t>
+          <t>Social issues, e.g. corruption, Family/children, Mental health</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr"/>
@@ -6815,7 +6815,7 @@
       <c r="O9" s="3" t="inlineStr"/>
       <c r="P9" s="3" t="inlineStr">
         <is>
-          <t>Mental health/emotional struggle, Kenyan or Nigerian political/social problems, General political/social/cultural problems, Men’s behavior</t>
+          <t>Kenyan or Nigerian political/social problems, Mental health/emotional struggle, Men's behavior, Global political/social/cultural problems</t>
         </is>
       </c>
       <c r="Q9" s="3" t="inlineStr"/>
@@ -6827,18 +6827,18 @@
       <c r="S9" s="3" t="inlineStr"/>
       <c r="T9" s="3" t="inlineStr">
         <is>
-          <t>Personal story, News/telling facts, Commentary/opinion</t>
+          <t>Commentary/opinion, News/telling facts, Personal story</t>
         </is>
       </c>
       <c r="U9" s="3" t="inlineStr"/>
       <c r="V9" s="3" t="inlineStr">
         <is>
-          <t>Information seeking, Self expression/identity construction</t>
+          <t>Self expression/identity construction, Information seeking</t>
         </is>
       </c>
       <c r="W9" s="3" t="inlineStr">
         <is>
-          <t>Personal experience, Cultural/social observations, Other</t>
+          <t>Cultural/social observations, Personal experience, Other</t>
         </is>
       </c>
       <c r="X9" s="3" t="inlineStr">
@@ -6848,7 +6848,7 @@
       </c>
       <c r="Y9" s="3" t="inlineStr">
         <is>
-          <t>Anecdotal examples, Presented as common sense, Other</t>
+          <t>Presented as common sense, Anecdotal examples, Other</t>
         </is>
       </c>
       <c r="Z9" s="3" t="inlineStr">
@@ -6909,7 +6909,7 @@
       <c r="F10" s="3" t="inlineStr"/>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>Family/children, Mental health, Social issues, e.g. corruption</t>
+          <t>Social issues, e.g. corruption, Family/children, Mental health</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr"/>
@@ -6954,24 +6954,24 @@
       <c r="S10" s="3" t="inlineStr"/>
       <c r="T10" s="3" t="inlineStr">
         <is>
-          <t>Personal story, Commentary/opinion</t>
+          <t>Commentary/opinion, Personal story</t>
         </is>
       </c>
       <c r="U10" s="3" t="inlineStr"/>
       <c r="V10" s="3" t="inlineStr">
         <is>
-          <t>Information seeking, Self expression/identity construction</t>
+          <t>Self expression/identity construction, Information seeking</t>
         </is>
       </c>
       <c r="W10" s="3" t="inlineStr">
         <is>
-          <t>Personal experience, Cultural/social observations</t>
+          <t>Cultural/social observations, Personal experience</t>
         </is>
       </c>
       <c r="X10" s="3" t="inlineStr"/>
       <c r="Y10" s="3" t="inlineStr">
         <is>
-          <t>Anecdotal examples, Presented as common sense</t>
+          <t>Presented as common sense, Anecdotal examples</t>
         </is>
       </c>
       <c r="Z10" s="3" t="inlineStr"/>
@@ -7028,7 +7028,7 @@
       <c r="F11" s="3" t="inlineStr"/>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>Mental health, Social Issues, e.g. corruption, Gender issues, e.g. equality, Religion/morality</t>
+          <t>Social issues, e.g. corruption, Gender issues, e.g. equality, Religion/morality, Mental health</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr"/>
@@ -7061,13 +7061,13 @@
       <c r="O11" s="3" t="inlineStr"/>
       <c r="P11" s="3" t="inlineStr">
         <is>
-          <t>Mental health/emotional struggle, General political/social/cultural problems, Men’s behavior</t>
+          <t>Mental health/emotional struggle, Men's behavior, Global political/social/cultural problems</t>
         </is>
       </c>
       <c r="Q11" s="3" t="inlineStr"/>
       <c r="R11" s="3" t="inlineStr">
         <is>
-          <t>Building community, More emotional growth/healing</t>
+          <t>More emotional growth/healing, Building community</t>
         </is>
       </c>
       <c r="S11" s="3" t="inlineStr"/>
@@ -7079,18 +7079,18 @@
       <c r="U11" s="3" t="inlineStr"/>
       <c r="V11" s="3" t="inlineStr">
         <is>
-          <t>Information seeking, Connection/social interaction, Self expression/identity construction</t>
+          <t>Self expression/identity construction, Connection/social interaction, Information seeking</t>
         </is>
       </c>
       <c r="W11" s="3" t="inlineStr">
         <is>
-          <t>Personal experience, Cultural/social observations</t>
+          <t>Cultural/social observations, Personal experience</t>
         </is>
       </c>
       <c r="X11" s="3" t="inlineStr"/>
       <c r="Y11" s="3" t="inlineStr">
         <is>
-          <t>Anecdotal examples, Presented as common sense</t>
+          <t>Presented as common sense, Anecdotal examples</t>
         </is>
       </c>
       <c r="Z11" s="3" t="inlineStr"/>
@@ -7159,7 +7159,7 @@
       <c r="F12" s="3" t="inlineStr"/>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>Gender issues, e.g. equality, Social issues, e.g. corruption</t>
+          <t>Social issues, e.g. corruption, Gender issues, e.g. equality</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr"/>
@@ -7192,7 +7192,7 @@
       <c r="O12" s="3" t="inlineStr"/>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t>Kenyan or Nigerian political/social problems, General political/social/cultural problems</t>
+          <t>Kenyan or Nigerian political/social problems, Global political/social/cultural problems</t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr"/>
@@ -7282,7 +7282,7 @@
       <c r="F13" s="3" t="inlineStr"/>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>Gender issues, e.g. equality, Social issues, e.g. corruption, Family/children</t>
+          <t>Social issues, e.g. corruption, Gender issues, e.g. equality, Family/children</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr"/>
@@ -7315,25 +7315,25 @@
       <c r="O13" s="3" t="inlineStr"/>
       <c r="P13" s="3" t="inlineStr">
         <is>
-          <t>Kenyan or Nigerian political/social problems, Women/feminism, General political/social/cultural problems</t>
+          <t>Kenyan or Nigerian political/social problems, Women/feminism, Global political/social/cultural problems</t>
         </is>
       </c>
       <c r="Q13" s="3" t="inlineStr"/>
       <c r="R13" s="3" t="inlineStr">
         <is>
-          <t>Social or political change, More equality/respect for women</t>
+          <t>More equality/respect for women, Social or political change</t>
         </is>
       </c>
       <c r="S13" s="3" t="inlineStr"/>
       <c r="T13" s="3" t="inlineStr">
         <is>
-          <t>Commentary/opinion, Advice/instruction</t>
+          <t>Advice/instruction, Commentary/opinion</t>
         </is>
       </c>
       <c r="U13" s="3" t="inlineStr"/>
       <c r="V13" s="3" t="inlineStr">
         <is>
-          <t>Information seeking, Self expression/identity construction</t>
+          <t>Self expression/identity construction, Information seeking</t>
         </is>
       </c>
       <c r="W13" s="3" t="inlineStr">
@@ -7375,7 +7375,7 @@
       </c>
       <c r="AF13" s="3" t="inlineStr">
         <is>
-          <t>Calls for men to follow more equitable gender norms, Calls for women to follow more equitable gender norms, Other</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="AG13" s="3" t="inlineStr">
@@ -7417,7 +7417,7 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>Gender issues, e.g. equality, Social issues, e.g. corruption</t>
+          <t>Social issues, e.g. corruption, Gender issues, e.g. equality</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr"/>
@@ -7450,7 +7450,7 @@
       <c r="O14" s="3" t="inlineStr"/>
       <c r="P14" s="3" t="inlineStr">
         <is>
-          <t>Women/feminism, General political/social/cultural problems</t>
+          <t>Women/feminism, Global political/social/cultural problems</t>
         </is>
       </c>
       <c r="Q14" s="3" t="inlineStr"/>
@@ -7462,24 +7462,24 @@
       <c r="S14" s="3" t="inlineStr"/>
       <c r="T14" s="3" t="inlineStr">
         <is>
-          <t>Personal story, Commentary/opinion</t>
+          <t>Commentary/opinion, Personal story</t>
         </is>
       </c>
       <c r="U14" s="3" t="inlineStr"/>
       <c r="V14" s="3" t="inlineStr">
         <is>
-          <t>Information seeking, Self expression/identity construction</t>
+          <t>Self expression/identity construction, Information seeking</t>
         </is>
       </c>
       <c r="W14" s="3" t="inlineStr">
         <is>
-          <t>Personal experience, Cultural/social observations</t>
+          <t>Cultural/social observations, Personal experience</t>
         </is>
       </c>
       <c r="X14" s="3" t="inlineStr"/>
       <c r="Y14" s="3" t="inlineStr">
         <is>
-          <t>Anecdotal examples, Presented as common sense</t>
+          <t>Presented as common sense, Anecdotal examples</t>
         </is>
       </c>
       <c r="Z14" s="3" t="inlineStr"/>
@@ -7569,7 +7569,7 @@
       <c r="O15" s="3" t="inlineStr"/>
       <c r="P15" s="3" t="inlineStr">
         <is>
-          <t>Kenyan or Nigerian political/social problems, General political/social/cultural problems</t>
+          <t>Kenyan or Nigerian political/social problems, Global political/social/cultural problems</t>
         </is>
       </c>
       <c r="Q15" s="3" t="inlineStr"/>
@@ -7581,13 +7581,13 @@
       <c r="S15" s="3" t="inlineStr"/>
       <c r="T15" s="3" t="inlineStr">
         <is>
-          <t>Commentary/opinion, Advice/instruction</t>
+          <t>Advice/instruction, Commentary/opinion</t>
         </is>
       </c>
       <c r="U15" s="3" t="inlineStr"/>
       <c r="V15" s="3" t="inlineStr">
         <is>
-          <t>Information seeking, Self expression/identity construction, Documentation of events</t>
+          <t>Self expression/identity construction, Documentation of events, Information seeking</t>
         </is>
       </c>
       <c r="W15" s="3" t="inlineStr">
@@ -7629,7 +7629,7 @@
       </c>
       <c r="AF15" s="3" t="inlineStr">
         <is>
-          <t>Calls for politicians or social figures to do something, Other</t>
+          <t>Other, Calls for political / social action</t>
         </is>
       </c>
       <c r="AG15" s="3" t="inlineStr">
@@ -7671,7 +7671,7 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>Dating/marriage, Gender issues, e.g. equality</t>
+          <t>Gender issues, e.g. equality, Dating/marriage</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr"/>
@@ -7698,13 +7698,13 @@
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t>Men need to dominate/lead, Men need to be fully self-reliant</t>
+          <t>Men need to be fully self-reliant, Men need to dominate/lead</t>
         </is>
       </c>
       <c r="O16" s="3" t="inlineStr"/>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t>Women/feminism, Men’s behavior</t>
+          <t>Women/feminism, Men's behavior</t>
         </is>
       </c>
       <c r="Q16" s="3" t="inlineStr"/>
@@ -7764,7 +7764,7 @@
       </c>
       <c r="AF16" s="3" t="inlineStr">
         <is>
-          <t>Calls for men to follow more traditional gender norms</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="AG16" s="3" t="inlineStr"/>
@@ -7802,7 +7802,7 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>Dating/marriage, Money/status, Gender issues, e.g. equality, Religion/morality</t>
+          <t>Gender issues, e.g. equality, Religion/morality, Dating/marriage, Money/status</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr"/>
@@ -7829,13 +7829,13 @@
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t>Men need to dominate/lead, Men need to provide/succeed</t>
+          <t>Men need to provide/succeed, Men need to dominate/lead</t>
         </is>
       </c>
       <c r="O17" s="3" t="inlineStr"/>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t>Women/feminism, Men’s behavior, Economic/status pressure</t>
+          <t>Economic/status pressure, Women/feminism, Men's behavior</t>
         </is>
       </c>
       <c r="Q17" s="3" t="inlineStr"/>
@@ -7853,7 +7853,7 @@
       <c r="U17" s="3" t="inlineStr"/>
       <c r="V17" s="3" t="inlineStr">
         <is>
-          <t>Entertainment/escapism, Self expression/identity construction, Status seeking</t>
+          <t>Self expression/identity construction, Entertainment/escapism, Status seeking</t>
         </is>
       </c>
       <c r="W17" s="3" t="inlineStr">
@@ -7864,7 +7864,7 @@
       <c r="X17" s="3" t="inlineStr"/>
       <c r="Y17" s="3" t="inlineStr">
         <is>
-          <t>No justification, Presented as common sense</t>
+          <t>Presented as common sense, No justification</t>
         </is>
       </c>
       <c r="Z17" s="3" t="inlineStr"/>
@@ -7895,7 +7895,7 @@
       </c>
       <c r="AF17" s="3" t="inlineStr">
         <is>
-          <t>Calls for women to follow more traditional gender norms, Other</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="AG17" s="3" t="inlineStr">
@@ -7929,13 +7929,13 @@
       <c r="F18" s="3" t="inlineStr"/>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>Money/status, Gender issues, Friends/socializing, Dating/marriage</t>
+          <t>Friends/socializing, Dating/marriage, Money/status, Gender issues, e.g. equality</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr"/>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>Interview/conversational content, Commentary/reaction content, Motivational/self-help content</t>
+          <t>Interview/conversational content, Motivational/self-help content, Commentary/reaction content</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr"/>
@@ -7956,13 +7956,13 @@
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t>Men need to dominate/lead, Men need to provide/succeed, Men need to improve themselves</t>
+          <t>Men need to improve themselves, Men need to provide/succeed, Men need to dominate/lead</t>
         </is>
       </c>
       <c r="O18" s="3" t="inlineStr"/>
       <c r="P18" s="3" t="inlineStr">
         <is>
-          <t>Women/feminism, Men’s behavior, Economic/status pressure</t>
+          <t>Economic/status pressure, Women/feminism, Men's behavior</t>
         </is>
       </c>
       <c r="Q18" s="3" t="inlineStr"/>
@@ -7984,7 +7984,7 @@
       <c r="U18" s="3" t="inlineStr"/>
       <c r="V18" s="3" t="inlineStr">
         <is>
-          <t>Self expression/identity construction, Status seeking, Entertainment/escapism</t>
+          <t>Self expression/identity construction, Entertainment/escapism, Status seeking</t>
         </is>
       </c>
       <c r="W18" s="3" t="inlineStr">
@@ -7995,7 +7995,7 @@
       <c r="X18" s="3" t="inlineStr"/>
       <c r="Y18" s="3" t="inlineStr">
         <is>
-          <t>Anecdotal examples, Presented as common sense</t>
+          <t>Presented as common sense, Anecdotal examples</t>
         </is>
       </c>
       <c r="Z18" s="3" t="inlineStr"/>
@@ -8026,7 +8026,7 @@
       </c>
       <c r="AF18" s="3" t="inlineStr">
         <is>
-          <t>Calls for men to follow more traditional gender norms, Other</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="AG18" s="3" t="inlineStr">
@@ -8060,7 +8060,7 @@
       <c r="F19" s="3" t="inlineStr"/>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>Gender issues, Religion/morality, Dating/marriage</t>
+          <t>Religion/morality, Dating/marriage, Gender issues, e.g. equality</t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr"/>
@@ -8087,13 +8087,13 @@
       </c>
       <c r="N19" s="3" t="inlineStr">
         <is>
-          <t>Men need to dominate/lead, Men are disadvantaged/victims</t>
+          <t>Men are disadvantaged/victims, Men need to dominate/lead</t>
         </is>
       </c>
       <c r="O19" s="3" t="inlineStr"/>
       <c r="P19" s="3" t="inlineStr">
         <is>
-          <t>Women/feminism, Men’s behavior, Other</t>
+          <t>Women/feminism, Men's behavior, Other</t>
         </is>
       </c>
       <c r="Q19" s="3" t="inlineStr">
@@ -8115,12 +8115,12 @@
       <c r="U19" s="3" t="inlineStr"/>
       <c r="V19" s="3" t="inlineStr">
         <is>
-          <t>Entertainment/escapism, Status seeking, Self expression/identity construction</t>
+          <t>Self expression/identity construction, Entertainment/escapism, Status seeking</t>
         </is>
       </c>
       <c r="W19" s="3" t="inlineStr">
         <is>
-          <t>Moral/religious claims, Generalizations about men/women</t>
+          <t>Generalizations about men/women, Moral/religious claims</t>
         </is>
       </c>
       <c r="X19" s="3" t="inlineStr"/>
@@ -8187,7 +8187,7 @@
       <c r="F20" s="3" t="inlineStr"/>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>Gender issues, Dating/marriage, Social issues, Money/status</t>
+          <t>Dating/marriage, Money/status, Gender issues, e.g. equality, Social issues, e.g. corruption</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr"/>
@@ -8220,7 +8220,7 @@
       <c r="O20" s="3" t="inlineStr"/>
       <c r="P20" s="3" t="inlineStr">
         <is>
-          <t>Women/feminism, General political/social/cultural problems, Other</t>
+          <t>Women/feminism, Other, Global political/social/cultural problems</t>
         </is>
       </c>
       <c r="Q20" s="3" t="inlineStr">
@@ -8242,7 +8242,7 @@
       <c r="U20" s="3" t="inlineStr"/>
       <c r="V20" s="3" t="inlineStr">
         <is>
-          <t>Entertainment/escapism, Status seeking, Self expression/identity construction</t>
+          <t>Self expression/identity construction, Entertainment/escapism, Status seeking</t>
         </is>
       </c>
       <c r="W20" s="3" t="inlineStr">
@@ -8253,7 +8253,7 @@
       <c r="X20" s="3" t="inlineStr"/>
       <c r="Y20" s="3" t="inlineStr">
         <is>
-          <t>No justification, Presented as common sense</t>
+          <t>Presented as common sense, No justification</t>
         </is>
       </c>
       <c r="Z20" s="3" t="inlineStr"/>
@@ -8314,7 +8314,7 @@
       <c r="F21" s="3" t="inlineStr"/>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>Dating/marriage, Gender issues, Family/children, Religion/morality</t>
+          <t>Religion/morality, Dating/marriage, Family/children, Gender issues, e.g. equality</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr"/>
@@ -8341,7 +8341,7 @@
       </c>
       <c r="N21" s="3" t="inlineStr">
         <is>
-          <t>Men need to dominate/lead, Men need to be fully self-reliant, Other</t>
+          <t>Men need to be fully self-reliant, Men need to dominate/lead, Other</t>
         </is>
       </c>
       <c r="O21" s="3" t="inlineStr">
@@ -8351,7 +8351,7 @@
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
-          <t>Men’s behavior</t>
+          <t>Men's behavior</t>
         </is>
       </c>
       <c r="Q21" s="3" t="inlineStr"/>
@@ -8369,7 +8369,7 @@
       <c r="U21" s="3" t="inlineStr"/>
       <c r="V21" s="3" t="inlineStr">
         <is>
-          <t>Entertainment/escapism, Status seeking, Self expression/identity construction</t>
+          <t>Self expression/identity construction, Entertainment/escapism, Status seeking</t>
         </is>
       </c>
       <c r="W21" s="3" t="inlineStr">
@@ -8380,7 +8380,7 @@
       <c r="X21" s="3" t="inlineStr"/>
       <c r="Y21" s="3" t="inlineStr">
         <is>
-          <t>No justification, Presented as common sense</t>
+          <t>Presented as common sense, No justification</t>
         </is>
       </c>
       <c r="Z21" s="3" t="inlineStr"/>
@@ -8437,7 +8437,7 @@
       <c r="F22" s="3" t="inlineStr"/>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>Dating/marriage, Gender issues, Family/children, Religion/morality</t>
+          <t>Religion/morality, Dating/marriage, Family/children, Gender issues, e.g. equality</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr"/>
@@ -8464,7 +8464,7 @@
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
-          <t>Men need to dominate/lead, Men need to provide/succeed, Other</t>
+          <t>Men need to provide/succeed, Men need to dominate/lead, Other</t>
         </is>
       </c>
       <c r="O22" s="3" t="inlineStr">
@@ -8474,7 +8474,7 @@
       </c>
       <c r="P22" s="3" t="inlineStr">
         <is>
-          <t>Men’s behavior, Other</t>
+          <t>Men's behavior, Other</t>
         </is>
       </c>
       <c r="Q22" s="3" t="inlineStr">
@@ -8500,12 +8500,12 @@
       <c r="U22" s="3" t="inlineStr"/>
       <c r="V22" s="3" t="inlineStr">
         <is>
-          <t>Entertainment/escapism, Status seeking, Self expression/identity construction</t>
+          <t>Self expression/identity construction, Entertainment/escapism, Status seeking</t>
         </is>
       </c>
       <c r="W22" s="3" t="inlineStr">
         <is>
-          <t>Generalizations about men/women, Moral/religious claims, Cultural/social observations</t>
+          <t>Generalizations about men/women, Cultural/social observations, Moral/religious claims</t>
         </is>
       </c>
       <c r="X22" s="3" t="inlineStr"/>
@@ -8542,7 +8542,7 @@
       </c>
       <c r="AF22" s="3" t="inlineStr">
         <is>
-          <t>Calls for men to follow more traditional gender norms, Other</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="AG22" s="3" t="inlineStr">
@@ -8576,7 +8576,7 @@
       <c r="F23" s="3" t="inlineStr"/>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>Dating/marriage, Family/children, Gender issues, Religion/morality</t>
+          <t>Religion/morality, Dating/marriage, Family/children, Gender issues, e.g. equality</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr"/>
@@ -8613,7 +8613,7 @@
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
-          <t>Women/feminism, Men’s behavior, Other</t>
+          <t>Women/feminism, Men's behavior, Other</t>
         </is>
       </c>
       <c r="Q23" s="3" t="inlineStr">
@@ -8639,7 +8639,7 @@
       <c r="U23" s="3" t="inlineStr"/>
       <c r="V23" s="3" t="inlineStr">
         <is>
-          <t>Entertainment/escapism, Status seeking, Self expression/identity construction</t>
+          <t>Self expression/identity construction, Entertainment/escapism, Status seeking</t>
         </is>
       </c>
       <c r="W23" s="3" t="inlineStr">
@@ -8650,7 +8650,7 @@
       <c r="X23" s="3" t="inlineStr"/>
       <c r="Y23" s="3" t="inlineStr">
         <is>
-          <t>No justification, Presented as common sense</t>
+          <t>Presented as common sense, No justification</t>
         </is>
       </c>
       <c r="Z23" s="3" t="inlineStr"/>
@@ -8715,7 +8715,7 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>Gender issues, Dating/marriage, Mental health</t>
+          <t>Dating/marriage, Mental health, Gender issues, e.g. equality</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr"/>
@@ -8764,13 +8764,13 @@
       </c>
       <c r="T24" s="3" t="inlineStr">
         <is>
-          <t>Advice/instruction, Commentary/opinion, Motivational speech</t>
+          <t>Motivational speech, Advice/instruction, Commentary/opinion</t>
         </is>
       </c>
       <c r="U24" s="3" t="inlineStr"/>
       <c r="V24" s="3" t="inlineStr">
         <is>
-          <t>Information seeking, Status seeking, Self expression/identity construction</t>
+          <t>Self expression/identity construction, Information seeking, Status seeking</t>
         </is>
       </c>
       <c r="W24" s="3" t="inlineStr">
@@ -8781,7 +8781,7 @@
       <c r="X24" s="3" t="inlineStr"/>
       <c r="Y24" s="3" t="inlineStr">
         <is>
-          <t>No justification, Presented as common sense</t>
+          <t>Presented as common sense, No justification</t>
         </is>
       </c>
       <c r="Z24" s="3" t="inlineStr"/>
@@ -8812,7 +8812,7 @@
       </c>
       <c r="AF24" s="3" t="inlineStr">
         <is>
-          <t>Calls for men to follow more traditional gender norms, Other</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="AG24" s="3" t="inlineStr">
@@ -8854,7 +8854,7 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>Gender issues, Dating/marriage</t>
+          <t>Dating/marriage, Gender issues, e.g. equality</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr"/>
@@ -8881,13 +8881,13 @@
       </c>
       <c r="N25" s="3" t="inlineStr">
         <is>
-          <t>Men need to dominate/lead, Men need to be fully self-reliant, Men need to not show emotions</t>
+          <t>Men need to be fully self-reliant, Men need to not show emotions, Men need to dominate/lead</t>
         </is>
       </c>
       <c r="O25" s="3" t="inlineStr"/>
       <c r="P25" s="3" t="inlineStr">
         <is>
-          <t>Men's behavior, Women/feminism</t>
+          <t>Women/feminism, Men's behavior</t>
         </is>
       </c>
       <c r="Q25" s="3" t="inlineStr"/>
@@ -8899,7 +8899,7 @@
       <c r="S25" s="3" t="inlineStr"/>
       <c r="T25" s="3" t="inlineStr">
         <is>
-          <t>Advice/instruction, Commentary/opinion, Motivational speech</t>
+          <t>Motivational speech, Advice/instruction, Commentary/opinion</t>
         </is>
       </c>
       <c r="U25" s="3" t="inlineStr"/>
@@ -8916,7 +8916,7 @@
       <c r="X25" s="3" t="inlineStr"/>
       <c r="Y25" s="3" t="inlineStr">
         <is>
-          <t>No justification, Presented as common sense</t>
+          <t>Presented as common sense, No justification</t>
         </is>
       </c>
       <c r="Z25" s="3" t="inlineStr"/>
@@ -8947,7 +8947,7 @@
       </c>
       <c r="AF25" s="3" t="inlineStr">
         <is>
-          <t>Calls for men to follow more traditional gender norms</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="AG25" s="3" t="inlineStr"/>
@@ -8975,7 +8975,7 @@
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>Other, Shares something surprising</t>
+          <t>Shares something surprising, Other</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
@@ -8985,7 +8985,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>Gender issues, Dating/marriage, Religion/morality</t>
+          <t>Religion/morality, Dating/marriage, Gender issues, e.g. equality</t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr"/>
@@ -9012,7 +9012,7 @@
       </c>
       <c r="N26" s="3" t="inlineStr">
         <is>
-          <t>Men need to dominate/lead, Men need to be fully self-reliant, Men need to not show emotions, Other</t>
+          <t>Men need to be fully self-reliant, Men need to not show emotions, Men need to dominate/lead, Other</t>
         </is>
       </c>
       <c r="O26" s="3" t="inlineStr">
@@ -9022,7 +9022,7 @@
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
-          <t>Men's behavior, Women/feminism, Other</t>
+          <t>Women/feminism, Men's behavior, Other</t>
         </is>
       </c>
       <c r="Q26" s="3" t="inlineStr">
@@ -9042,7 +9042,7 @@
       </c>
       <c r="T26" s="3" t="inlineStr">
         <is>
-          <t>Advice/instruction, Commentary/opinion, Motivational speech</t>
+          <t>Motivational speech, Advice/instruction, Commentary/opinion</t>
         </is>
       </c>
       <c r="U26" s="3" t="inlineStr"/>
@@ -9090,7 +9090,7 @@
       </c>
       <c r="AF26" s="3" t="inlineStr">
         <is>
-          <t>Calls for men to follow more traditional gender norms, Other</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="AG26" s="3" t="inlineStr">
@@ -9132,7 +9132,7 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>Gender issues, Dating/marriage, Religion/morality</t>
+          <t>Religion/morality, Dating/marriage, Gender issues, e.g. equality</t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr"/>
@@ -9159,7 +9159,7 @@
       </c>
       <c r="N27" s="3" t="inlineStr">
         <is>
-          <t>Men need to dominate/lead, Men need to be fully self-reliant, Other</t>
+          <t>Men need to be fully self-reliant, Men need to dominate/lead, Other</t>
         </is>
       </c>
       <c r="O27" s="3" t="inlineStr">
@@ -9169,7 +9169,7 @@
       </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
-          <t>Men's behavior, Women/feminism</t>
+          <t>Women/feminism, Men's behavior</t>
         </is>
       </c>
       <c r="Q27" s="3" t="inlineStr"/>
@@ -9185,7 +9185,7 @@
       </c>
       <c r="T27" s="3" t="inlineStr">
         <is>
-          <t>Advice/instruction, Commentary/opinion, Motivational speech</t>
+          <t>Motivational speech, Advice/instruction, Commentary/opinion</t>
         </is>
       </c>
       <c r="U27" s="3" t="inlineStr"/>
@@ -9233,7 +9233,7 @@
       </c>
       <c r="AF27" s="3" t="inlineStr">
         <is>
-          <t>Calls for men to follow more traditional gender norms, Other</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="AG27" s="3" t="inlineStr">
@@ -9265,13 +9265,13 @@
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>Use of all CAPS, Uses a news headline or social media trend as opener, Shares something surprising, Shares something sexual</t>
+          <t>Uses a news headline or social media trend as opener, Shares something surprising, Shares something sexual, Use of all CAPS</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr"/>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>Gender issues, Dating/marriage, Religion/morality, Social issues, Mental health</t>
+          <t>Religion/morality, Dating/marriage, Mental health, Gender issues, e.g. equality, Social issues, e.g. corruption</t>
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr"/>
@@ -9298,7 +9298,7 @@
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
-          <t>Men need to improve themselves, Men need to be fully self-reliant, Other</t>
+          <t>Men need to be fully self-reliant, Men need to improve themselves, Other</t>
         </is>
       </c>
       <c r="O28" s="3" t="inlineStr">
@@ -9308,7 +9308,7 @@
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
-          <t>Men's behavior, Women/feminism, Mental health/emotional struggle, Other</t>
+          <t>Mental health/emotional struggle, Women/feminism, Men's behavior, Other</t>
         </is>
       </c>
       <c r="Q28" s="3" t="inlineStr">
@@ -9334,12 +9334,12 @@
       <c r="U28" s="3" t="inlineStr"/>
       <c r="V28" s="3" t="inlineStr">
         <is>
-          <t>Information seeking, Self expression/identity construction, Status seeking</t>
+          <t>Self expression/identity construction, Information seeking, Status seeking</t>
         </is>
       </c>
       <c r="W28" s="3" t="inlineStr">
         <is>
-          <t>Generalizations about men/women, Moral/religious claims, Facts/statistics, Cultural/social observations</t>
+          <t>Generalizations about men/women, Cultural/social observations, Moral/religious claims, Facts/statistics</t>
         </is>
       </c>
       <c r="X28" s="3" t="inlineStr"/>
@@ -9376,7 +9376,7 @@
       </c>
       <c r="AF28" s="3" t="inlineStr">
         <is>
-          <t>Calls for men to follow more traditional gender norms, Other</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="AG28" s="3" t="inlineStr">
@@ -9418,7 +9418,7 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>Money/status, Dating/marriage, Gender issues</t>
+          <t>Dating/marriage, Money/status, Gender issues, e.g. equality</t>
         </is>
       </c>
       <c r="H29" s="3" t="inlineStr"/>
@@ -9445,25 +9445,25 @@
       </c>
       <c r="N29" s="3" t="inlineStr">
         <is>
-          <t>Men need to provide/succeed, Men need to be fully self-reliant</t>
+          <t>Men need to be fully self-reliant, Men need to provide/succeed</t>
         </is>
       </c>
       <c r="O29" s="3" t="inlineStr"/>
       <c r="P29" s="3" t="inlineStr">
         <is>
-          <t>Men’s behavior, Economic/status pressure</t>
+          <t>Economic/status pressure, Men's behavior</t>
         </is>
       </c>
       <c r="Q29" s="3" t="inlineStr"/>
       <c r="R29" s="3" t="inlineStr">
         <is>
-          <t>More wealth/status, More self-discipline/fitness</t>
+          <t>More self-discipline/fitness, More wealth/status</t>
         </is>
       </c>
       <c r="S29" s="3" t="inlineStr"/>
       <c r="T29" s="3" t="inlineStr">
         <is>
-          <t>Advice/instruction, Commentary/opinion, Motivational speech</t>
+          <t>Motivational speech, Advice/instruction, Commentary/opinion</t>
         </is>
       </c>
       <c r="U29" s="3" t="inlineStr"/>
@@ -9511,7 +9511,7 @@
       </c>
       <c r="AF29" s="3" t="inlineStr">
         <is>
-          <t>Calls for men to follow more traditional gender norms</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="AG29" s="3" t="inlineStr"/>
@@ -9549,7 +9549,7 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>Religion/morality, Dating/marriage, Gender issues</t>
+          <t>Religion/morality, Dating/marriage, Gender issues, e.g. equality</t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr"/>
@@ -9576,7 +9576,7 @@
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
-          <t>Men need to dominate/lead, Men need to not show emotion, Other</t>
+          <t>Men need to dominate/lead, Other, Men need to not show emotions</t>
         </is>
       </c>
       <c r="O30" s="3" t="inlineStr">
@@ -9606,7 +9606,7 @@
       </c>
       <c r="T30" s="3" t="inlineStr">
         <is>
-          <t>Advice/instruction, Commentary/opinion, Motivational speech</t>
+          <t>Motivational speech, Advice/instruction, Commentary/opinion</t>
         </is>
       </c>
       <c r="U30" s="3" t="inlineStr"/>
@@ -9654,7 +9654,7 @@
       </c>
       <c r="AF30" s="3" t="inlineStr">
         <is>
-          <t>Calls for men to follow more traditional gender norms, Other</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="AG30" s="3" t="inlineStr">
@@ -9696,7 +9696,7 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>Religion/morality, Dating/marriage, Gender issues, Family/children</t>
+          <t>Religion/morality, Dating/marriage, Family/children, Gender issues, e.g. equality</t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr"/>
@@ -9723,7 +9723,7 @@
       </c>
       <c r="N31" s="3" t="inlineStr">
         <is>
-          <t>Men need to dominate/lead, Men need to provide/succeed, Other</t>
+          <t>Men need to provide/succeed, Men need to dominate/lead, Other</t>
         </is>
       </c>
       <c r="O31" s="3" t="inlineStr">
@@ -9753,7 +9753,7 @@
       </c>
       <c r="T31" s="3" t="inlineStr">
         <is>
-          <t>Advice/instruction, Commentary/opinion, Motivational speech</t>
+          <t>Motivational speech, Advice/instruction, Commentary/opinion</t>
         </is>
       </c>
       <c r="U31" s="3" t="inlineStr"/>
@@ -9764,13 +9764,13 @@
       </c>
       <c r="W31" s="3" t="inlineStr">
         <is>
-          <t>Moral/religious claims, Generalizations about men/women</t>
+          <t>Generalizations about men/women, Moral/religious claims</t>
         </is>
       </c>
       <c r="X31" s="3" t="inlineStr"/>
       <c r="Y31" s="3" t="inlineStr">
         <is>
-          <t>Presented as common sense, References religion/tradition</t>
+          <t>References religion/tradition, Presented as common sense</t>
         </is>
       </c>
       <c r="Z31" s="3" t="inlineStr"/>
@@ -9801,7 +9801,7 @@
       </c>
       <c r="AF31" s="3" t="inlineStr">
         <is>
-          <t>Calls for men to follow more traditional gender norms, Calls for women to follow more traditional gender norms, Other</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="AG31" s="3" t="inlineStr">
@@ -9843,7 +9843,7 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>Money/status, Dating/marriage, Gender issues, Family/children</t>
+          <t>Dating/marriage, Family/children, Money/status, Gender issues, e.g. equality</t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr"/>
@@ -9880,7 +9880,7 @@
       </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
-          <t>Women/feminism, Men’s behavior, Economic/status pressure, Other</t>
+          <t>Economic/status pressure, Women/feminism, Men's behavior, Other</t>
         </is>
       </c>
       <c r="Q32" s="3" t="inlineStr">
@@ -9900,7 +9900,7 @@
       </c>
       <c r="T32" s="3" t="inlineStr">
         <is>
-          <t>Advice/instruction, Commentary/opinion, Motivational speech</t>
+          <t>Motivational speech, Advice/instruction, Commentary/opinion</t>
         </is>
       </c>
       <c r="U32" s="3" t="inlineStr"/>
@@ -9911,13 +9911,13 @@
       </c>
       <c r="W32" s="3" t="inlineStr">
         <is>
-          <t>Cultural/social observations, Generalizations about men/women</t>
+          <t>Generalizations about men/women, Cultural/social observations</t>
         </is>
       </c>
       <c r="X32" s="3" t="inlineStr"/>
       <c r="Y32" s="3" t="inlineStr">
         <is>
-          <t>No justification, Presented as common sense</t>
+          <t>Presented as common sense, No justification</t>
         </is>
       </c>
       <c r="Z32" s="3" t="inlineStr"/>
@@ -9948,7 +9948,7 @@
       </c>
       <c r="AF32" s="3" t="inlineStr">
         <is>
-          <t>Calls for men to follow more traditional gender norms, Other</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="AG32" s="3" t="inlineStr">
@@ -9982,7 +9982,7 @@
       <c r="F33" s="3" t="inlineStr"/>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>Dating/marriage, Gender issues</t>
+          <t>Dating/marriage, Gender issues, e.g. equality</t>
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr"/>
@@ -10015,7 +10015,7 @@
       <c r="O33" s="3" t="inlineStr"/>
       <c r="P33" s="3" t="inlineStr">
         <is>
-          <t>Women/feminism, Men’s behavior</t>
+          <t>Women/feminism, Men's behavior</t>
         </is>
       </c>
       <c r="Q33" s="3" t="inlineStr"/>
@@ -10033,7 +10033,7 @@
       <c r="U33" s="3" t="inlineStr"/>
       <c r="V33" s="3" t="inlineStr">
         <is>
-          <t>Self expression/identity construction, Status seeking, Entertainment/escapism</t>
+          <t>Self expression/identity construction, Entertainment/escapism, Status seeking</t>
         </is>
       </c>
       <c r="W33" s="3" t="inlineStr">
@@ -10044,7 +10044,7 @@
       <c r="X33" s="3" t="inlineStr"/>
       <c r="Y33" s="3" t="inlineStr">
         <is>
-          <t>No justification, Presented as common sense</t>
+          <t>Presented as common sense, No justification</t>
         </is>
       </c>
       <c r="Z33" s="3" t="inlineStr"/>
@@ -10075,7 +10075,7 @@
       </c>
       <c r="AF33" s="3" t="inlineStr">
         <is>
-          <t>Calls for men to follow more traditional gender norms, Calls for women to follow more traditional gender norms, Other</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="AG33" s="3" t="inlineStr">
@@ -10109,7 +10109,7 @@
       <c r="F34" s="3" t="inlineStr"/>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>Mental health, Dating/marriage</t>
+          <t>Dating/marriage, Mental health</t>
         </is>
       </c>
       <c r="H34" s="3" t="inlineStr"/>
@@ -10142,7 +10142,7 @@
       <c r="O34" s="3" t="inlineStr"/>
       <c r="P34" s="3" t="inlineStr">
         <is>
-          <t>Mental health/emotional struggle, Men’s behavior</t>
+          <t>Mental health/emotional struggle, Men's behavior</t>
         </is>
       </c>
       <c r="Q34" s="3" t="inlineStr"/>
@@ -10160,7 +10160,7 @@
       <c r="U34" s="3" t="inlineStr"/>
       <c r="V34" s="3" t="inlineStr">
         <is>
-          <t>Information seeking, Self expression/identity construction</t>
+          <t>Self expression/identity construction, Information seeking</t>
         </is>
       </c>
       <c r="W34" s="3" t="inlineStr">
@@ -10228,7 +10228,7 @@
       <c r="F35" s="3" t="inlineStr"/>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>Family/children, Mental health, Social issues</t>
+          <t>Family/children, Mental health, Social issues, e.g. corruption</t>
         </is>
       </c>
       <c r="H35" s="3" t="inlineStr"/>
@@ -10261,7 +10261,7 @@
       <c r="O35" s="3" t="inlineStr"/>
       <c r="P35" s="3" t="inlineStr">
         <is>
-          <t>Mental health/emotional struggle, General political/social/cultural problems</t>
+          <t>Mental health/emotional struggle, Global political/social/cultural problems</t>
         </is>
       </c>
       <c r="Q35" s="3" t="inlineStr"/>
@@ -10273,13 +10273,13 @@
       <c r="S35" s="3" t="inlineStr"/>
       <c r="T35" s="3" t="inlineStr">
         <is>
-          <t>Commentary/opinion, Advice/instruction</t>
+          <t>Advice/instruction, Commentary/opinion</t>
         </is>
       </c>
       <c r="U35" s="3" t="inlineStr"/>
       <c r="V35" s="3" t="inlineStr">
         <is>
-          <t>Information seeking, Connection/social interaction</t>
+          <t>Connection/social interaction, Information seeking</t>
         </is>
       </c>
       <c r="W35" s="3" t="inlineStr">
@@ -10347,7 +10347,7 @@
       <c r="F36" s="3" t="inlineStr"/>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>Gender issues, Mental health, Friends/socializing</t>
+          <t>Friends/socializing, Mental health, Gender issues, e.g. equality</t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr"/>
@@ -10374,7 +10374,7 @@
       </c>
       <c r="N36" s="3" t="inlineStr">
         <is>
-          <t>Men need to improve themselves, Men need to be emotionally open, Other</t>
+          <t>Men need to be emotionally open, Men need to improve themselves, Other</t>
         </is>
       </c>
       <c r="O36" s="3" t="inlineStr">
@@ -10384,7 +10384,7 @@
       </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
-          <t>General political/social/cultural problems, Mental health/emotional struggle</t>
+          <t>Mental health/emotional struggle, Global political/social/cultural problems</t>
         </is>
       </c>
       <c r="Q36" s="3" t="inlineStr"/>
@@ -10400,13 +10400,13 @@
       </c>
       <c r="T36" s="3" t="inlineStr">
         <is>
-          <t>Commentary/opinion, Advice/instruction, Motivational speech</t>
+          <t>Motivational speech, Advice/instruction, Commentary/opinion</t>
         </is>
       </c>
       <c r="U36" s="3" t="inlineStr"/>
       <c r="V36" s="3" t="inlineStr">
         <is>
-          <t>Connection/social interaction, Self expression/identity construction</t>
+          <t>Self expression/identity construction, Connection/social interaction</t>
         </is>
       </c>
       <c r="W36" s="3" t="inlineStr">
@@ -10448,7 +10448,7 @@
       </c>
       <c r="AF36" s="3" t="inlineStr">
         <is>
-          <t>Calls for men to follow more equitable gender norms, Other</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="AG36" s="3" t="inlineStr">
@@ -10482,7 +10482,7 @@
       <c r="F37" s="3" t="inlineStr"/>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>Gender issues, Social issues, Money/status</t>
+          <t>Money/status, Gender issues, e.g. equality, Social issues, e.g. corruption</t>
         </is>
       </c>
       <c r="H37" s="3" t="inlineStr"/>
@@ -10515,7 +10515,7 @@
       <c r="O37" s="3" t="inlineStr"/>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t>Women/feminism, Kenyan or Nigerian political/social problems, General political/social/cultural problems, Other</t>
+          <t>Kenyan or Nigerian political/social problems, Women/feminism, Other, Global political/social/cultural problems</t>
         </is>
       </c>
       <c r="Q37" s="3" t="inlineStr">
@@ -10537,7 +10537,7 @@
       <c r="U37" s="3" t="inlineStr"/>
       <c r="V37" s="3" t="inlineStr">
         <is>
-          <t>Information seeking, Self expression/identity construction</t>
+          <t>Self expression/identity construction, Information seeking</t>
         </is>
       </c>
       <c r="W37" s="3" t="inlineStr">
@@ -10605,7 +10605,7 @@
       <c r="F38" s="3" t="inlineStr"/>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>Mental health, Friends/socializing, Gender issues</t>
+          <t>Friends/socializing, Mental health, Gender issues, e.g. equality</t>
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr"/>
@@ -10642,13 +10642,13 @@
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
-          <t>Mental health/emotional struggle, Men’s behavior</t>
+          <t>Mental health/emotional struggle, Men's behavior</t>
         </is>
       </c>
       <c r="Q38" s="3" t="inlineStr"/>
       <c r="R38" s="3" t="inlineStr">
         <is>
-          <t>Building community, More emotional growth/healing</t>
+          <t>More emotional growth/healing, Building community</t>
         </is>
       </c>
       <c r="S38" s="3" t="inlineStr"/>
@@ -10660,18 +10660,18 @@
       <c r="U38" s="3" t="inlineStr"/>
       <c r="V38" s="3" t="inlineStr">
         <is>
-          <t>Information seeking, Self expression/identity construction, Connection/social interaction</t>
+          <t>Self expression/identity construction, Connection/social interaction, Information seeking</t>
         </is>
       </c>
       <c r="W38" s="3" t="inlineStr">
         <is>
-          <t>Personal experience, Cultural/social observations</t>
+          <t>Cultural/social observations, Personal experience</t>
         </is>
       </c>
       <c r="X38" s="3" t="inlineStr"/>
       <c r="Y38" s="3" t="inlineStr">
         <is>
-          <t>Anecdotal examples, Presented as common sense</t>
+          <t>Presented as common sense, Anecdotal examples</t>
         </is>
       </c>
       <c r="Z38" s="3" t="inlineStr"/>
@@ -10702,7 +10702,7 @@
       </c>
       <c r="AF38" s="3" t="inlineStr">
         <is>
-          <t>Calls for men to follow more equitable gender norms, Other</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="AG38" s="3" t="inlineStr">
@@ -10736,7 +10736,7 @@
       <c r="F39" s="3" t="inlineStr"/>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>Mental health, Social issues</t>
+          <t>Mental health, Social issues, e.g. corruption</t>
         </is>
       </c>
       <c r="H39" s="3" t="inlineStr"/>
@@ -10769,7 +10769,7 @@
       <c r="O39" s="3" t="inlineStr"/>
       <c r="P39" s="3" t="inlineStr">
         <is>
-          <t>Men’s behavior, Mental health/emotional struggle</t>
+          <t>Mental health/emotional struggle, Men's behavior</t>
         </is>
       </c>
       <c r="Q39" s="3" t="inlineStr"/>
@@ -10787,7 +10787,7 @@
       <c r="U39" s="3" t="inlineStr"/>
       <c r="V39" s="3" t="inlineStr">
         <is>
-          <t>Information seeking, Self expression/identity construction</t>
+          <t>Self expression/identity construction, Information seeking</t>
         </is>
       </c>
       <c r="W39" s="3" t="inlineStr">
@@ -10871,7 +10871,7 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>Gender issues, Social issues, Friends/socializing, Other</t>
+          <t>Friends/socializing, Other, Gender issues, e.g. equality, Social issues, e.g. corruption</t>
         </is>
       </c>
       <c r="H40" s="3" t="inlineStr">
@@ -10912,7 +10912,7 @@
       </c>
       <c r="P40" s="3" t="inlineStr">
         <is>
-          <t>Women/feminism, General political/social/cultural problems, Other</t>
+          <t>Women/feminism, Other, Global political/social/cultural problems</t>
         </is>
       </c>
       <c r="Q40" s="3" t="inlineStr">
@@ -10932,7 +10932,7 @@
       </c>
       <c r="T40" s="3" t="inlineStr">
         <is>
-          <t>Commentary/opinion, Motivational speech</t>
+          <t>Motivational speech, Commentary/opinion</t>
         </is>
       </c>
       <c r="U40" s="3" t="inlineStr"/>
@@ -10949,7 +10949,7 @@
       <c r="X40" s="3" t="inlineStr"/>
       <c r="Y40" s="3" t="inlineStr">
         <is>
-          <t>No justification, Presented as common sense</t>
+          <t>Presented as common sense, No justification</t>
         </is>
       </c>
       <c r="Z40" s="3" t="inlineStr"/>
@@ -10980,7 +10980,7 @@
       </c>
       <c r="AF40" s="3" t="inlineStr">
         <is>
-          <t>Calls for men to follow more traditional gender norms, Other</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="AG40" s="3" t="inlineStr">
@@ -11014,7 +11014,7 @@
       <c r="F41" s="3" t="inlineStr"/>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>Gender issues, Social issues, Gaming/technology, Family/children</t>
+          <t>Gaming/technology, Family/children, Gender issues, e.g. equality, Social issues, e.g. corruption</t>
         </is>
       </c>
       <c r="H41" s="3" t="inlineStr"/>
@@ -11047,7 +11047,7 @@
       <c r="O41" s="3" t="inlineStr"/>
       <c r="P41" s="3" t="inlineStr">
         <is>
-          <t>General political/social/cultural problems, Western political/social influence, Other</t>
+          <t>Western political/social influence, Other, Global political/social/cultural problems</t>
         </is>
       </c>
       <c r="Q41" s="3" t="inlineStr">
@@ -11069,7 +11069,7 @@
       <c r="U41" s="3" t="inlineStr"/>
       <c r="V41" s="3" t="inlineStr">
         <is>
-          <t>Information seeking, Self expression/identity construction</t>
+          <t>Self expression/identity construction, Information seeking</t>
         </is>
       </c>
       <c r="W41" s="3" t="inlineStr">

--- a/Codebooks/Human Codebooks/content - cleaned/D - Content Analysis Codebook (cleaned) - Selene.xlsx
+++ b/Codebooks/Human Codebooks/content - cleaned/D - Content Analysis Codebook (cleaned) - Selene.xlsx
@@ -2595,7 +2595,7 @@
       </c>
       <c r="AF17" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Other, Calls for men to follow more traditional gender norms</t>
         </is>
       </c>
       <c r="AG17" s="3" t="inlineStr">
@@ -2730,7 +2730,7 @@
       </c>
       <c r="AF18" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Other, Calls for men to follow more traditional gender norms</t>
         </is>
       </c>
       <c r="AG18" s="3" t="inlineStr">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="AF21" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Other, Calls for men to follow more traditional gender norms</t>
         </is>
       </c>
       <c r="AG21" s="3" t="inlineStr">
@@ -4020,7 +4020,7 @@
       </c>
       <c r="AF28" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Other, Calls for men to follow more traditional gender norms</t>
         </is>
       </c>
       <c r="AG28" s="3" t="inlineStr">
@@ -4806,7 +4806,7 @@
       </c>
       <c r="AF34" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Calls for women to follow more traditional gender norms</t>
         </is>
       </c>
       <c r="AG34" s="3" t="inlineStr"/>
@@ -5556,7 +5556,7 @@
       </c>
       <c r="AF40" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Other, Calls for men to follow more equitable gender norms</t>
         </is>
       </c>
       <c r="AG40" s="3" t="inlineStr">
@@ -7375,7 +7375,7 @@
       </c>
       <c r="AF13" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Other, Calls for men to follow more equitable gender norms, Calls for women to follow more equitable gender norms</t>
         </is>
       </c>
       <c r="AG13" s="3" t="inlineStr">
@@ -7764,7 +7764,7 @@
       </c>
       <c r="AF16" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Calls for men to follow more traditional gender norms</t>
         </is>
       </c>
       <c r="AG16" s="3" t="inlineStr"/>
@@ -7895,7 +7895,7 @@
       </c>
       <c r="AF17" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Other, Calls for women to follow more traditional gender norms</t>
         </is>
       </c>
       <c r="AG17" s="3" t="inlineStr">
@@ -8026,7 +8026,7 @@
       </c>
       <c r="AF18" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Other, Calls for men to follow more traditional gender norms</t>
         </is>
       </c>
       <c r="AG18" s="3" t="inlineStr">
@@ -8542,7 +8542,7 @@
       </c>
       <c r="AF22" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Other, Calls for men to follow more traditional gender norms</t>
         </is>
       </c>
       <c r="AG22" s="3" t="inlineStr">
@@ -8812,7 +8812,7 @@
       </c>
       <c r="AF24" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Other, Calls for men to follow more traditional gender norms</t>
         </is>
       </c>
       <c r="AG24" s="3" t="inlineStr">
@@ -8947,7 +8947,7 @@
       </c>
       <c r="AF25" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Calls for men to follow more traditional gender norms</t>
         </is>
       </c>
       <c r="AG25" s="3" t="inlineStr"/>
@@ -9090,7 +9090,7 @@
       </c>
       <c r="AF26" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Other, Calls for men to follow more traditional gender norms</t>
         </is>
       </c>
       <c r="AG26" s="3" t="inlineStr">
@@ -9233,7 +9233,7 @@
       </c>
       <c r="AF27" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Other, Calls for men to follow more traditional gender norms</t>
         </is>
       </c>
       <c r="AG27" s="3" t="inlineStr">
@@ -9376,7 +9376,7 @@
       </c>
       <c r="AF28" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Other, Calls for men to follow more traditional gender norms</t>
         </is>
       </c>
       <c r="AG28" s="3" t="inlineStr">
@@ -9511,7 +9511,7 @@
       </c>
       <c r="AF29" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Calls for men to follow more traditional gender norms</t>
         </is>
       </c>
       <c r="AG29" s="3" t="inlineStr"/>
@@ -9654,7 +9654,7 @@
       </c>
       <c r="AF30" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Other, Calls for men to follow more traditional gender norms</t>
         </is>
       </c>
       <c r="AG30" s="3" t="inlineStr">
@@ -9801,7 +9801,7 @@
       </c>
       <c r="AF31" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Other, Calls for men to follow more traditional gender norms, Calls for women to follow more traditional gender norms</t>
         </is>
       </c>
       <c r="AG31" s="3" t="inlineStr">
@@ -9948,7 +9948,7 @@
       </c>
       <c r="AF32" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Other, Calls for men to follow more traditional gender norms</t>
         </is>
       </c>
       <c r="AG32" s="3" t="inlineStr">
@@ -10075,7 +10075,7 @@
       </c>
       <c r="AF33" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Other, Calls for men to follow more traditional gender norms, Calls for women to follow more traditional gender norms</t>
         </is>
       </c>
       <c r="AG33" s="3" t="inlineStr">
@@ -10448,7 +10448,7 @@
       </c>
       <c r="AF36" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Other, Calls for men to follow more equitable gender norms</t>
         </is>
       </c>
       <c r="AG36" s="3" t="inlineStr">
@@ -10702,7 +10702,7 @@
       </c>
       <c r="AF38" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Other, Calls for men to follow more equitable gender norms</t>
         </is>
       </c>
       <c r="AG38" s="3" t="inlineStr">
@@ -10980,7 +10980,7 @@
       </c>
       <c r="AF40" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Other, Calls for men to follow more traditional gender norms</t>
         </is>
       </c>
       <c r="AG40" s="3" t="inlineStr">

--- a/Codebooks/Human Codebooks/content - cleaned/D - Content Analysis Codebook (cleaned) - Selene.xlsx
+++ b/Codebooks/Human Codebooks/content - cleaned/D - Content Analysis Codebook (cleaned) - Selene.xlsx
@@ -450,42 +450,42 @@
   <dimension ref="A1:AG41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="45" customWidth="1" min="2" max="2"/>
-    <col width="45" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="28" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="28" customWidth="1" min="7" max="7"/>
-    <col width="28" customWidth="1" min="8" max="8"/>
-    <col width="28" customWidth="1" min="9" max="9"/>
-    <col width="28" customWidth="1" min="10" max="10"/>
-    <col width="28" customWidth="1" min="11" max="11"/>
-    <col width="28" customWidth="1" min="12" max="12"/>
-    <col width="28" customWidth="1" min="13" max="13"/>
-    <col width="28" customWidth="1" min="14" max="14"/>
-    <col width="28" customWidth="1" min="15" max="15"/>
-    <col width="28" customWidth="1" min="16" max="16"/>
-    <col width="28" customWidth="1" min="17" max="17"/>
-    <col width="28" customWidth="1" min="18" max="18"/>
-    <col width="28" customWidth="1" min="19" max="19"/>
-    <col width="28" customWidth="1" min="20" max="20"/>
-    <col width="28" customWidth="1" min="21" max="21"/>
-    <col width="28" customWidth="1" min="22" max="22"/>
-    <col width="28" customWidth="1" min="23" max="23"/>
-    <col width="28" customWidth="1" min="24" max="24"/>
-    <col width="28" customWidth="1" min="25" max="25"/>
-    <col width="28" customWidth="1" min="26" max="26"/>
-    <col width="28" customWidth="1" min="27" max="27"/>
-    <col width="28" customWidth="1" min="28" max="28"/>
-    <col width="28" customWidth="1" min="29" max="29"/>
-    <col width="28" customWidth="1" min="30" max="30"/>
-    <col width="28" customWidth="1" min="31" max="31"/>
-    <col width="28" customWidth="1" min="32" max="32"/>
-    <col width="28" customWidth="1" min="33" max="33"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="26" customWidth="1" min="7" max="7"/>
+    <col width="26" customWidth="1" min="8" max="8"/>
+    <col width="26" customWidth="1" min="9" max="9"/>
+    <col width="26" customWidth="1" min="10" max="10"/>
+    <col width="26" customWidth="1" min="11" max="11"/>
+    <col width="26" customWidth="1" min="12" max="12"/>
+    <col width="26" customWidth="1" min="13" max="13"/>
+    <col width="26" customWidth="1" min="14" max="14"/>
+    <col width="26" customWidth="1" min="15" max="15"/>
+    <col width="26" customWidth="1" min="16" max="16"/>
+    <col width="26" customWidth="1" min="17" max="17"/>
+    <col width="26" customWidth="1" min="18" max="18"/>
+    <col width="26" customWidth="1" min="19" max="19"/>
+    <col width="26" customWidth="1" min="20" max="20"/>
+    <col width="26" customWidth="1" min="21" max="21"/>
+    <col width="26" customWidth="1" min="22" max="22"/>
+    <col width="26" customWidth="1" min="23" max="23"/>
+    <col width="26" customWidth="1" min="24" max="24"/>
+    <col width="26" customWidth="1" min="25" max="25"/>
+    <col width="26" customWidth="1" min="26" max="26"/>
+    <col width="26" customWidth="1" min="27" max="27"/>
+    <col width="26" customWidth="1" min="28" max="28"/>
+    <col width="26" customWidth="1" min="29" max="29"/>
+    <col width="26" customWidth="1" min="30" max="30"/>
+    <col width="26" customWidth="1" min="31" max="31"/>
+    <col width="26" customWidth="1" min="32" max="32"/>
+    <col width="26" customWidth="1" min="33" max="33"/>
   </cols>
   <sheetData>
-    <row r="1" ht="60" customHeight="1">
+    <row r="1" ht="48" customHeight="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
           <t>Content ID</t>
@@ -5702,42 +5702,42 @@
   <dimension ref="A1:AG41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="45" customWidth="1" min="2" max="2"/>
-    <col width="45" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="28" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="28" customWidth="1" min="7" max="7"/>
-    <col width="28" customWidth="1" min="8" max="8"/>
-    <col width="28" customWidth="1" min="9" max="9"/>
-    <col width="28" customWidth="1" min="10" max="10"/>
-    <col width="28" customWidth="1" min="11" max="11"/>
-    <col width="28" customWidth="1" min="12" max="12"/>
-    <col width="28" customWidth="1" min="13" max="13"/>
-    <col width="28" customWidth="1" min="14" max="14"/>
-    <col width="28" customWidth="1" min="15" max="15"/>
-    <col width="28" customWidth="1" min="16" max="16"/>
-    <col width="28" customWidth="1" min="17" max="17"/>
-    <col width="28" customWidth="1" min="18" max="18"/>
-    <col width="28" customWidth="1" min="19" max="19"/>
-    <col width="28" customWidth="1" min="20" max="20"/>
-    <col width="28" customWidth="1" min="21" max="21"/>
-    <col width="28" customWidth="1" min="22" max="22"/>
-    <col width="28" customWidth="1" min="23" max="23"/>
-    <col width="28" customWidth="1" min="24" max="24"/>
-    <col width="28" customWidth="1" min="25" max="25"/>
-    <col width="28" customWidth="1" min="26" max="26"/>
-    <col width="28" customWidth="1" min="27" max="27"/>
-    <col width="28" customWidth="1" min="28" max="28"/>
-    <col width="28" customWidth="1" min="29" max="29"/>
-    <col width="28" customWidth="1" min="30" max="30"/>
-    <col width="28" customWidth="1" min="31" max="31"/>
-    <col width="28" customWidth="1" min="32" max="32"/>
-    <col width="28" customWidth="1" min="33" max="33"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="26" customWidth="1" min="7" max="7"/>
+    <col width="26" customWidth="1" min="8" max="8"/>
+    <col width="26" customWidth="1" min="9" max="9"/>
+    <col width="26" customWidth="1" min="10" max="10"/>
+    <col width="26" customWidth="1" min="11" max="11"/>
+    <col width="26" customWidth="1" min="12" max="12"/>
+    <col width="26" customWidth="1" min="13" max="13"/>
+    <col width="26" customWidth="1" min="14" max="14"/>
+    <col width="26" customWidth="1" min="15" max="15"/>
+    <col width="26" customWidth="1" min="16" max="16"/>
+    <col width="26" customWidth="1" min="17" max="17"/>
+    <col width="26" customWidth="1" min="18" max="18"/>
+    <col width="26" customWidth="1" min="19" max="19"/>
+    <col width="26" customWidth="1" min="20" max="20"/>
+    <col width="26" customWidth="1" min="21" max="21"/>
+    <col width="26" customWidth="1" min="22" max="22"/>
+    <col width="26" customWidth="1" min="23" max="23"/>
+    <col width="26" customWidth="1" min="24" max="24"/>
+    <col width="26" customWidth="1" min="25" max="25"/>
+    <col width="26" customWidth="1" min="26" max="26"/>
+    <col width="26" customWidth="1" min="27" max="27"/>
+    <col width="26" customWidth="1" min="28" max="28"/>
+    <col width="26" customWidth="1" min="29" max="29"/>
+    <col width="26" customWidth="1" min="30" max="30"/>
+    <col width="26" customWidth="1" min="31" max="31"/>
+    <col width="26" customWidth="1" min="32" max="32"/>
+    <col width="26" customWidth="1" min="33" max="33"/>
   </cols>
   <sheetData>
-    <row r="1" ht="60" customHeight="1">
+    <row r="1" ht="48" customHeight="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
           <t>Content ID</t>
